--- a/server/data/Solar Panel Application 2019-now.xlsx
+++ b/server/data/Solar Panel Application 2019-now.xlsx
@@ -61279,10 +61279,10 @@
         <v>28</v>
       </c>
       <c r="P754" s="10">
-        <v>32.372999999999998</v>
+        <v>32.3056539905629</v>
       </c>
       <c r="Q754" s="10">
-        <v>-64.756603999999996</v>
+        <v>-64.78817544197068</v>
       </c>
     </row>
     <row r="755" spans="1:17" ht="90" customHeight="1" x14ac:dyDescent="0.25">

--- a/server/data/Solar Panel Application 2019-now.xlsx
+++ b/server/data/Solar Panel Application 2019-now.xlsx
@@ -568,10 +568,10 @@
         <v>Yes</v>
       </c>
       <c r="P2">
-        <v>32.370337</v>
+        <v>32.3632247</v>
       </c>
       <c r="Q2">
-        <v>-64.662784</v>
+        <v>-64.6778274</v>
       </c>
     </row>
     <row r="3" xml:space="preserve">
@@ -622,10 +622,10 @@
         <v>Yes</v>
       </c>
       <c r="P3">
-        <v>32.3795954</v>
+        <v>32.379602</v>
       </c>
       <c r="Q3">
-        <v>-64.6798981</v>
+        <v>-64.6799249</v>
       </c>
     </row>
     <row r="4" xml:space="preserve">
@@ -838,10 +838,10 @@
         <v>Yes</v>
       </c>
       <c r="P7">
-        <v>32.2896781</v>
+        <v>32.282015</v>
       </c>
       <c r="Q7">
-        <v>-64.7642965</v>
+        <v>-64.77564</v>
       </c>
     </row>
     <row r="8" xml:space="preserve">
@@ -949,10 +949,10 @@
         <v>Yes</v>
       </c>
       <c r="P9">
-        <v>32.3087506</v>
+        <v>32.3092928</v>
       </c>
       <c r="Q9">
-        <v>-64.7345598</v>
+        <v>-64.7335728</v>
       </c>
     </row>
     <row r="10" xml:space="preserve">
@@ -1057,10 +1057,10 @@
         <v>Yes</v>
       </c>
       <c r="P11">
-        <v>32.3337718</v>
+        <v>32.333312</v>
       </c>
       <c r="Q11">
-        <v>-64.6837334</v>
+        <v>-64.688369</v>
       </c>
     </row>
     <row r="12" xml:space="preserve">
@@ -1165,10 +1165,10 @@
         <v>Yes</v>
       </c>
       <c r="P13">
-        <v>32.2981931</v>
+        <v>32.2953411</v>
       </c>
       <c r="Q13">
-        <v>-64.862352</v>
+        <v>-64.8629142</v>
       </c>
     </row>
     <row r="14" xml:space="preserve">
@@ -1219,10 +1219,10 @@
         <v>Yes</v>
       </c>
       <c r="P14">
-        <v>32.2956001</v>
+        <v>32.2942516</v>
       </c>
       <c r="Q14">
-        <v>-64.7900269</v>
+        <v>-64.7880402</v>
       </c>
     </row>
     <row r="15" xml:space="preserve">
@@ -1327,10 +1327,10 @@
         <v>Yes</v>
       </c>
       <c r="P16">
-        <v>32.2983597</v>
+        <v>32.294539</v>
       </c>
       <c r="Q16">
-        <v>-64.8623751</v>
+        <v>-64.869691</v>
       </c>
     </row>
     <row r="17" xml:space="preserve">
@@ -1489,10 +1489,10 @@
         <v>Yes</v>
       </c>
       <c r="P19">
-        <v>32.2584617</v>
+        <v>32.2580681</v>
       </c>
       <c r="Q19">
-        <v>-64.8211233</v>
+        <v>-64.8209506</v>
       </c>
     </row>
     <row r="20" xml:space="preserve">
@@ -1543,10 +1543,10 @@
         <v>Yes</v>
       </c>
       <c r="P20">
-        <v>32.3118689</v>
+        <v>32.30203</v>
       </c>
       <c r="Q20">
-        <v>-64.7485771</v>
+        <v>-64.757146</v>
       </c>
     </row>
     <row r="21" xml:space="preserve">
@@ -2031,10 +2031,10 @@
         <v>Yes</v>
       </c>
       <c r="P29">
-        <v>32.260736</v>
+        <v>32.2544361</v>
       </c>
       <c r="Q29">
-        <v>-64.830029</v>
+        <v>-64.8439449</v>
       </c>
     </row>
     <row r="30" xml:space="preserve">
@@ -2085,10 +2085,10 @@
         <v>Yes</v>
       </c>
       <c r="P30">
-        <v>32.3222624</v>
+        <v>32.3224614</v>
       </c>
       <c r="Q30">
-        <v>-64.7248685</v>
+        <v>-64.7214824</v>
       </c>
     </row>
     <row r="31" xml:space="preserve">
@@ -2139,10 +2139,10 @@
         <v>Yes</v>
       </c>
       <c r="P31">
-        <v>32.2776505</v>
+        <v>32.277112</v>
       </c>
       <c r="Q31">
-        <v>-64.781677</v>
+        <v>-64.781423</v>
       </c>
     </row>
     <row r="32" xml:space="preserve">
@@ -2193,10 +2193,10 @@
         <v>Yes</v>
       </c>
       <c r="P32">
-        <v>32.2543371</v>
+        <v>32.2535982</v>
       </c>
       <c r="Q32">
-        <v>-64.8435591</v>
+        <v>-64.8536045</v>
       </c>
     </row>
     <row r="33" xml:space="preserve">
@@ -2412,10 +2412,10 @@
         <v>Yes</v>
       </c>
       <c r="P36">
-        <v>32.286077</v>
+        <v>32.2857855</v>
       </c>
       <c r="Q36">
-        <v>-64.770124</v>
+        <v>-64.7690394</v>
       </c>
     </row>
     <row r="37" xml:space="preserve">
@@ -2468,10 +2468,10 @@
         <v>Yes</v>
       </c>
       <c r="P37">
-        <v>32.3255161</v>
+        <v>32.3249511</v>
       </c>
       <c r="Q37">
-        <v>-64.7412199</v>
+        <v>-64.7410545</v>
       </c>
     </row>
     <row r="38" xml:space="preserve">
@@ -2522,10 +2522,10 @@
         <v>Yes</v>
       </c>
       <c r="P38">
-        <v>32.2631567</v>
+        <v>32.2604984</v>
       </c>
       <c r="Q38">
-        <v>-64.805297</v>
+        <v>-64.8180176</v>
       </c>
     </row>
     <row r="39" xml:space="preserve">
@@ -2576,10 +2576,10 @@
         <v>Yes</v>
       </c>
       <c r="P39">
-        <v>32.250338</v>
+        <v>32.248964</v>
       </c>
       <c r="Q39">
-        <v>-64.848699</v>
+        <v>-64.839529</v>
       </c>
     </row>
     <row r="40" xml:space="preserve">
@@ -2684,10 +2684,10 @@
         <v>Yes</v>
       </c>
       <c r="P41">
-        <v>32.2808345</v>
+        <v>32.269838</v>
       </c>
       <c r="Q41">
-        <v>-64.7962048</v>
+        <v>-64.816052</v>
       </c>
     </row>
     <row r="42" xml:space="preserve">
@@ -2738,10 +2738,10 @@
         <v>Yes</v>
       </c>
       <c r="P42">
-        <v>32.269325</v>
+        <v>32.2688561</v>
       </c>
       <c r="Q42">
-        <v>-64.790744</v>
+        <v>-64.7904782</v>
       </c>
     </row>
     <row r="43" xml:space="preserve">
@@ -2956,10 +2956,10 @@
         <v>Yes</v>
       </c>
       <c r="P46">
-        <v>32.3044057</v>
+        <v>32.3042559</v>
       </c>
       <c r="Q46">
-        <v>-64.7991857</v>
+        <v>-64.7988335</v>
       </c>
     </row>
     <row r="47" xml:space="preserve">
@@ -3338,10 +3338,10 @@
         <v>Yes</v>
       </c>
       <c r="P53">
-        <v>32.282623</v>
+        <v>32.2849567</v>
       </c>
       <c r="Q53">
-        <v>-64.800339</v>
+        <v>-64.7753406</v>
       </c>
     </row>
     <row r="54" xml:space="preserve">
@@ -3446,10 +3446,10 @@
         <v>Yes</v>
       </c>
       <c r="P55">
-        <v>32.282095</v>
+        <v>32.2849567</v>
       </c>
       <c r="Q55">
-        <v>-64.801389</v>
+        <v>-64.7753406</v>
       </c>
     </row>
     <row r="56" xml:space="preserve">
@@ -3771,10 +3771,10 @@
         <v>Yes</v>
       </c>
       <c r="P61">
-        <v>32.3815884</v>
+        <v>32.3815816</v>
       </c>
       <c r="Q61">
-        <v>-64.6669631</v>
+        <v>-64.6669837</v>
       </c>
     </row>
     <row r="62" xml:space="preserve">
@@ -4153,10 +4153,10 @@
         <v>Yes</v>
       </c>
       <c r="P68">
-        <v>32.378457</v>
+        <v>32.3778111</v>
       </c>
       <c r="Q68">
-        <v>-64.685103</v>
+        <v>-64.6851087</v>
       </c>
     </row>
     <row r="69" xml:space="preserve">
@@ -4315,10 +4315,10 @@
         <v>Yes</v>
       </c>
       <c r="P71">
-        <v>32.2899416</v>
+        <v>32.290426</v>
       </c>
       <c r="Q71">
-        <v>-64.772349</v>
+        <v>-64.772063</v>
       </c>
     </row>
     <row r="72" xml:space="preserve">
@@ -4369,10 +4369,10 @@
         <v>Yes</v>
       </c>
       <c r="P72">
-        <v>32.2922687</v>
+        <v>32.291779</v>
       </c>
       <c r="Q72">
-        <v>-64.7678844</v>
+        <v>-64.767231</v>
       </c>
     </row>
     <row r="73" xml:space="preserve">
@@ -4423,10 +4423,10 @@
         <v>Yes</v>
       </c>
       <c r="P73">
-        <v>32.2925451</v>
+        <v>32.292488</v>
       </c>
       <c r="Q73">
-        <v>-64.7875355</v>
+        <v>-64.7874752</v>
       </c>
     </row>
     <row r="74" xml:space="preserve">
@@ -4477,10 +4477,10 @@
         <v>Yes</v>
       </c>
       <c r="P74">
-        <v>32.2614822</v>
+        <v>32.249392</v>
       </c>
       <c r="Q74">
-        <v>-64.8029824</v>
+        <v>-64.844169</v>
       </c>
     </row>
     <row r="75" xml:space="preserve">
@@ -4585,10 +4585,10 @@
         <v>Yes</v>
       </c>
       <c r="P76">
-        <v>32.2941285</v>
+        <v>32.2953502</v>
       </c>
       <c r="Q76">
-        <v>-64.7997008</v>
+        <v>-64.8027044</v>
       </c>
     </row>
     <row r="77" xml:space="preserve">
@@ -4639,10 +4639,10 @@
         <v>Yes</v>
       </c>
       <c r="P77">
-        <v>32.3158961</v>
+        <v>32.318016</v>
       </c>
       <c r="Q77">
-        <v>-64.7248843</v>
+        <v>-64.724186</v>
       </c>
     </row>
     <row r="78" xml:space="preserve">
@@ -4747,10 +4747,10 @@
         <v>Yes</v>
       </c>
       <c r="P79">
-        <v>32.27758</v>
+        <v>32.276417</v>
       </c>
       <c r="Q79">
-        <v>-64.787245</v>
+        <v>-64.788316</v>
       </c>
     </row>
     <row r="80" xml:space="preserve">
@@ -5287,10 +5287,10 @@
         <v>Yes</v>
       </c>
       <c r="P89">
-        <v>32.33713</v>
+        <v>32.336619</v>
       </c>
       <c r="Q89">
-        <v>-64.7316489</v>
+        <v>-64.731023</v>
       </c>
     </row>
     <row r="90" xml:space="preserve">
@@ -5449,10 +5449,10 @@
         <v>Yes</v>
       </c>
       <c r="P92">
-        <v>32.2803718</v>
+        <v>32.280183</v>
       </c>
       <c r="Q92">
-        <v>-64.7836317</v>
+        <v>-64.784913</v>
       </c>
     </row>
     <row r="93" xml:space="preserve">
@@ -5503,10 +5503,10 @@
         <v>Yes</v>
       </c>
       <c r="P93">
-        <v>32.273048</v>
+        <v>32.2678602</v>
       </c>
       <c r="Q93">
-        <v>-64.794697</v>
+        <v>-64.8053367</v>
       </c>
     </row>
     <row r="94" xml:space="preserve">
@@ -5614,10 +5614,10 @@
         <v>Yes</v>
       </c>
       <c r="P95">
-        <v>32.2596779</v>
+        <v>32.2594416</v>
       </c>
       <c r="Q95">
-        <v>-64.8661032</v>
+        <v>-64.8661233</v>
       </c>
     </row>
     <row r="96" xml:space="preserve">
@@ -5776,10 +5776,10 @@
         <v>Yes</v>
       </c>
       <c r="P98">
-        <v>32.2941</v>
+        <v>32.2969152</v>
       </c>
       <c r="Q98">
-        <v>-64.7963</v>
+        <v>-64.7944164</v>
       </c>
     </row>
     <row r="99" xml:space="preserve">
@@ -5887,10 +5887,10 @@
         <v>Yes</v>
       </c>
       <c r="P100">
-        <v>32.2808345</v>
+        <v>32.270992</v>
       </c>
       <c r="Q100">
-        <v>-64.7962048</v>
+        <v>-64.813991</v>
       </c>
     </row>
     <row r="101" xml:space="preserve">
@@ -6108,10 +6108,10 @@
         <v>Yes</v>
       </c>
       <c r="P104">
-        <v>32.297394</v>
+        <v>32.298507</v>
       </c>
       <c r="Q104">
-        <v>-64.866133</v>
+        <v>-64.863986</v>
       </c>
     </row>
     <row r="105" xml:space="preserve">
@@ -6270,10 +6270,10 @@
         <v>Yes</v>
       </c>
       <c r="P107">
-        <v>32.25866</v>
+        <v>32.258812</v>
       </c>
       <c r="Q107">
-        <v>-64.827887</v>
+        <v>-64.831001</v>
       </c>
     </row>
     <row r="108" xml:space="preserve">
@@ -6324,10 +6324,10 @@
         <v>Yes</v>
       </c>
       <c r="P108">
-        <v>32.277717</v>
+        <v>32.2777809</v>
       </c>
       <c r="Q108">
-        <v>-64.794515</v>
+        <v>-64.7942622</v>
       </c>
     </row>
     <row r="109" xml:space="preserve">
@@ -6869,10 +6869,10 @@
         <v>Yes</v>
       </c>
       <c r="P118">
-        <v>32.319887</v>
+        <v>32.320226</v>
       </c>
       <c r="Q118">
-        <v>-64.739033</v>
+        <v>-64.7395011</v>
       </c>
     </row>
     <row r="119" xml:space="preserve">
@@ -6977,10 +6977,10 @@
         <v>Yes</v>
       </c>
       <c r="P120">
-        <v>32.291189</v>
+        <v>32.289628</v>
       </c>
       <c r="Q120">
-        <v>-64.766623</v>
+        <v>-64.766077</v>
       </c>
     </row>
     <row r="121" xml:space="preserve">
@@ -7088,10 +7088,10 @@
         <v>Yes</v>
       </c>
       <c r="P122">
-        <v>32.282192</v>
+        <v>32.2834138</v>
       </c>
       <c r="Q122">
-        <v>-64.790646</v>
+        <v>-64.7930616</v>
       </c>
     </row>
     <row r="123" xml:space="preserve">
@@ -7252,10 +7252,10 @@
         <v>Yes</v>
       </c>
       <c r="P125">
-        <v>32.289049</v>
+        <v>32.288709</v>
       </c>
       <c r="Q125">
-        <v>-64.773041</v>
+        <v>-64.77274</v>
       </c>
     </row>
     <row r="126" xml:space="preserve">
@@ -7306,10 +7306,10 @@
         <v>Yes</v>
       </c>
       <c r="P126">
-        <v>32.2528267</v>
+        <v>32.252556</v>
       </c>
       <c r="Q126">
-        <v>-64.8345101</v>
+        <v>-64.838157</v>
       </c>
     </row>
     <row r="127" xml:space="preserve">
@@ -7523,10 +7523,10 @@
         <v>Yes</v>
       </c>
       <c r="P130">
-        <v>32.265839</v>
+        <v>32.2678602</v>
       </c>
       <c r="Q130">
-        <v>-64.829075</v>
+        <v>-64.8053367</v>
       </c>
     </row>
     <row r="131" xml:space="preserve">
@@ -7793,10 +7793,10 @@
         <v>Yes</v>
       </c>
       <c r="P135">
-        <v>32.307083</v>
+        <v>32.3065822</v>
       </c>
       <c r="Q135">
-        <v>-64.811466</v>
+        <v>-64.8113916</v>
       </c>
     </row>
     <row r="136" xml:space="preserve">
@@ -7955,10 +7955,10 @@
         <v>Yes</v>
       </c>
       <c r="P138">
-        <v>32.299717</v>
+        <v>32.29916</v>
       </c>
       <c r="Q138">
-        <v>-64.747314</v>
+        <v>-64.7501123</v>
       </c>
     </row>
     <row r="139" xml:space="preserve">
@@ -8009,10 +8009,10 @@
         <v>Yes</v>
       </c>
       <c r="P139">
-        <v>32.280364</v>
+        <v>32.2796943</v>
       </c>
       <c r="Q139">
-        <v>-64.789032</v>
+        <v>-64.78902</v>
       </c>
     </row>
     <row r="140" xml:space="preserve">
@@ -8170,11 +8170,11 @@
       <c r="O142" t="str">
         <v>Yes</v>
       </c>
-      <c r="P142" t="str">
-        <v>32.291840433333334</v>
+      <c r="P142">
+        <v>32.2884612</v>
       </c>
       <c r="Q142">
-        <v>-64.7637586333333</v>
+        <v>-64.7620789</v>
       </c>
     </row>
     <row r="143" xml:space="preserve">
@@ -8279,10 +8279,10 @@
         <v>Yes</v>
       </c>
       <c r="P144">
-        <v>32.2799048</v>
+        <v>32.279714</v>
       </c>
       <c r="Q144">
-        <v>-64.7861847</v>
+        <v>-64.786672</v>
       </c>
     </row>
     <row r="145" xml:space="preserve">
@@ -8386,11 +8386,11 @@
       <c r="O146" t="str">
         <v>Yes</v>
       </c>
-      <c r="P146" t="str">
-        <v>32.252626811111114</v>
+      <c r="P146">
+        <v>32.2535266</v>
       </c>
       <c r="Q146">
-        <v>-64.845693</v>
+        <v>-64.8485129</v>
       </c>
     </row>
     <row r="147" xml:space="preserve">
@@ -8711,10 +8711,10 @@
         <v>Yes</v>
       </c>
       <c r="P152">
-        <v>32.303719</v>
+        <v>32.302289</v>
       </c>
       <c r="Q152">
-        <v>-64.754045</v>
+        <v>-64.753397</v>
       </c>
     </row>
     <row r="153" xml:space="preserve">
@@ -8765,10 +8765,10 @@
         <v>Yes</v>
       </c>
       <c r="P153">
-        <v>32.300855</v>
+        <v>32.3010628</v>
       </c>
       <c r="Q153">
-        <v>-64.794857</v>
+        <v>-64.7938283</v>
       </c>
     </row>
     <row r="154" xml:space="preserve">
@@ -8873,10 +8873,10 @@
         <v>Yes</v>
       </c>
       <c r="P155">
-        <v>32.368196</v>
+        <v>32.3632247</v>
       </c>
       <c r="Q155">
-        <v>-64.673791</v>
+        <v>-64.6778274</v>
       </c>
     </row>
     <row r="156" xml:space="preserve">
@@ -9035,10 +9035,10 @@
         <v>Yes</v>
       </c>
       <c r="P158">
-        <v>32.3315121</v>
+        <v>32.333198</v>
       </c>
       <c r="Q158">
-        <v>-64.7112575</v>
+        <v>-64.707918</v>
       </c>
     </row>
     <row r="159" xml:space="preserve">
@@ -9360,10 +9360,10 @@
         <v>Yes</v>
       </c>
       <c r="P164">
-        <v>32.333328</v>
+        <v>32.3412801</v>
       </c>
       <c r="Q164">
-        <v>-64.727405</v>
+        <v>-64.7255713</v>
       </c>
     </row>
     <row r="165" xml:space="preserve">
@@ -9523,10 +9523,10 @@
         <v>Yes</v>
       </c>
       <c r="P167">
-        <v>32.2920063</v>
+        <v>32.2920166</v>
       </c>
       <c r="Q167">
-        <v>-64.8039222</v>
+        <v>-64.8039268</v>
       </c>
     </row>
     <row r="168" xml:space="preserve">
@@ -9632,10 +9632,10 @@
         <v>Yes</v>
       </c>
       <c r="P169">
-        <v>32.281492</v>
+        <v>32.2849567</v>
       </c>
       <c r="Q169">
-        <v>-64.80354</v>
+        <v>-64.7753406</v>
       </c>
     </row>
     <row r="170" xml:space="preserve">
@@ -9686,10 +9686,10 @@
         <v>Yes</v>
       </c>
       <c r="P170">
-        <v>32.296397</v>
+        <v>32.3008022</v>
       </c>
       <c r="Q170">
-        <v>-64.799038</v>
+        <v>-64.7915912</v>
       </c>
     </row>
     <row r="171" xml:space="preserve">
@@ -9906,10 +9906,10 @@
         <v>Yes</v>
       </c>
       <c r="P174">
-        <v>32.3071978</v>
+        <v>32.306682</v>
       </c>
       <c r="Q174">
-        <v>-64.7402722</v>
+        <v>-64.740254</v>
       </c>
     </row>
     <row r="175" xml:space="preserve">
@@ -9960,10 +9960,10 @@
         <v>Yes</v>
       </c>
       <c r="P175">
-        <v>32.29584</v>
+        <v>32.2963798</v>
       </c>
       <c r="Q175">
-        <v>-64.781915</v>
+        <v>-64.7815961</v>
       </c>
     </row>
     <row r="176" xml:space="preserve">
@@ -10290,10 +10290,10 @@
         <v>Yes</v>
       </c>
       <c r="P181">
-        <v>32.300171</v>
+        <v>32.301044</v>
       </c>
       <c r="Q181">
-        <v>-64.769805</v>
+        <v>-64.768792</v>
       </c>
     </row>
     <row r="182" xml:space="preserve">
@@ -10399,10 +10399,10 @@
         <v>Yes</v>
       </c>
       <c r="P183">
-        <v>32.341404</v>
+        <v>32.341832</v>
       </c>
       <c r="Q183">
-        <v>-64.729135</v>
+        <v>-64.729369</v>
       </c>
     </row>
     <row r="184" xml:space="preserve">
@@ -10453,10 +10453,10 @@
         <v>Yes</v>
       </c>
       <c r="P184">
-        <v>32.28383</v>
+        <v>32.280533</v>
       </c>
       <c r="Q184">
-        <v>-64.7866553</v>
+        <v>-64.792226</v>
       </c>
     </row>
     <row r="185" xml:space="preserve">
@@ -10727,10 +10727,10 @@
         <v>Yes</v>
       </c>
       <c r="P189">
-        <v>32.279869</v>
+        <v>32.279571</v>
       </c>
       <c r="Q189">
-        <v>-64.874234</v>
+        <v>-64.874619</v>
       </c>
     </row>
     <row r="190" xml:space="preserve">
@@ -10997,10 +10997,10 @@
         <v>Yes</v>
       </c>
       <c r="P194">
-        <v>32.2923572</v>
+        <v>32.29234</v>
       </c>
       <c r="Q194">
-        <v>-64.791171</v>
+        <v>-64.794984</v>
       </c>
     </row>
     <row r="195" xml:space="preserve">
@@ -11105,10 +11105,10 @@
         <v>Yes</v>
       </c>
       <c r="P196">
-        <v>32.312129</v>
+        <v>32.3113752</v>
       </c>
       <c r="Q196">
-        <v>-64.745703</v>
+        <v>-64.7458923</v>
       </c>
     </row>
     <row r="197" xml:space="preserve">
@@ -11213,10 +11213,10 @@
         <v>Yes</v>
       </c>
       <c r="P198">
-        <v>32.29732</v>
+        <v>32.29686</v>
       </c>
       <c r="Q198">
-        <v>-64.78297</v>
+        <v>-64.780142</v>
       </c>
     </row>
     <row r="199" xml:space="preserve">
@@ -11429,10 +11429,10 @@
         <v>Yes</v>
       </c>
       <c r="P202">
-        <v>32.3036953</v>
+        <v>32.320005</v>
       </c>
       <c r="Q202">
-        <v>-64.7558272</v>
+        <v>-64.734883</v>
       </c>
     </row>
     <row r="203" xml:space="preserve">
@@ -11810,10 +11810,10 @@
         <v>Yes</v>
       </c>
       <c r="P209">
-        <v>32.3183028</v>
+        <v>32.320607</v>
       </c>
       <c r="Q209">
-        <v>-64.7387109</v>
+        <v>-64.741398</v>
       </c>
     </row>
     <row r="210" xml:space="preserve">
@@ -11864,10 +11864,10 @@
         <v>Yes</v>
       </c>
       <c r="P210">
-        <v>32.252663</v>
+        <v>32.2532001</v>
       </c>
       <c r="Q210">
-        <v>-64.824422</v>
+        <v>-64.8243495</v>
       </c>
     </row>
     <row r="211" xml:space="preserve">
@@ -11918,10 +11918,10 @@
         <v>Yes</v>
       </c>
       <c r="P211">
-        <v>32.2548832</v>
+        <v>32.255716</v>
       </c>
       <c r="Q211">
-        <v>-64.8406697</v>
+        <v>-64.83705</v>
       </c>
     </row>
     <row r="212" xml:space="preserve">
@@ -12026,10 +12026,10 @@
         <v>Yes</v>
       </c>
       <c r="P213">
-        <v>32.250189</v>
+        <v>32.248954</v>
       </c>
       <c r="Q213">
-        <v>-64.849057</v>
+        <v>-64.844145</v>
       </c>
     </row>
     <row r="214" xml:space="preserve">
@@ -12134,10 +12134,10 @@
         <v>Yes</v>
       </c>
       <c r="P215">
-        <v>32.2548832</v>
+        <v>32.253657</v>
       </c>
       <c r="Q215">
-        <v>-64.8406697</v>
+        <v>-64.847854</v>
       </c>
     </row>
     <row r="216" xml:space="preserve">
@@ -12626,10 +12626,10 @@
         <v>Yes</v>
       </c>
       <c r="P224">
-        <v>32.2927587</v>
+        <v>32.2927844</v>
       </c>
       <c r="Q224">
-        <v>-64.7895377</v>
+        <v>-64.7895495</v>
       </c>
     </row>
     <row r="225" xml:space="preserve">
@@ -12789,10 +12789,10 @@
         <v>Yes</v>
       </c>
       <c r="P227">
-        <v>32.3175347</v>
+        <v>32.3163615</v>
       </c>
       <c r="Q227">
-        <v>-64.7463399666666</v>
+        <v>-64.7462481</v>
       </c>
     </row>
     <row r="228" xml:space="preserve">
@@ -12843,10 +12843,10 @@
         <v>Yes</v>
       </c>
       <c r="P228">
-        <v>32.270226</v>
+        <v>32.266766</v>
       </c>
       <c r="Q228">
-        <v>-64.804049</v>
+        <v>-64.8088</v>
       </c>
     </row>
     <row r="229" xml:space="preserve">
@@ -13005,10 +13005,10 @@
         <v>Yes</v>
       </c>
       <c r="P231">
-        <v>32.32193</v>
+        <v>32.324886</v>
       </c>
       <c r="Q231">
-        <v>-64.7253145</v>
+        <v>-64.715552</v>
       </c>
     </row>
     <row r="232" xml:space="preserve">
@@ -13059,10 +13059,10 @@
         <v>Yes</v>
       </c>
       <c r="P232">
-        <v>32.325188</v>
+        <v>32.324435</v>
       </c>
       <c r="Q232">
-        <v>-64.715632</v>
+        <v>-64.715038</v>
       </c>
     </row>
     <row r="233" xml:space="preserve">
@@ -13708,10 +13708,10 @@
         <v>Yes</v>
       </c>
       <c r="P244">
-        <v>32.3375</v>
+        <v>32.3412801</v>
       </c>
       <c r="Q244">
-        <v>-64.70222</v>
+        <v>-64.7255713</v>
       </c>
     </row>
     <row r="245" xml:space="preserve">
@@ -14307,10 +14307,10 @@
         <v>Yes</v>
       </c>
       <c r="P255">
-        <v>32.319887</v>
+        <v>32.320226</v>
       </c>
       <c r="Q255">
-        <v>-64.739033</v>
+        <v>-64.7395011</v>
       </c>
     </row>
     <row r="256" xml:space="preserve">
@@ -14361,10 +14361,10 @@
         <v>Yes</v>
       </c>
       <c r="P256">
-        <v>32.3039374</v>
+        <v>32.2942516</v>
       </c>
       <c r="Q256">
-        <v>-64.7591087</v>
+        <v>-64.7880402</v>
       </c>
     </row>
     <row r="257" xml:space="preserve">
@@ -14415,10 +14415,10 @@
         <v>Yes</v>
       </c>
       <c r="P257">
-        <v>32.279783</v>
+        <v>32.2794681</v>
       </c>
       <c r="Q257">
-        <v>-64.873973</v>
+        <v>-64.8749615</v>
       </c>
     </row>
     <row r="258" xml:space="preserve">
@@ -14523,10 +14523,10 @@
         <v>Yes</v>
       </c>
       <c r="P259">
-        <v>32.295074</v>
+        <v>32.2955659</v>
       </c>
       <c r="Q259">
-        <v>-64.775279</v>
+        <v>-64.7735148</v>
       </c>
     </row>
     <row r="260" xml:space="preserve">
@@ -14956,10 +14956,10 @@
         <v>Yes</v>
       </c>
       <c r="P267">
-        <v>32.31643</v>
+        <v>32.315555</v>
       </c>
       <c r="Q267">
-        <v>-64.720511</v>
+        <v>-64.721756</v>
       </c>
     </row>
     <row r="268" xml:space="preserve">
@@ -15387,11 +15387,11 @@
       <c r="O275" t="str">
         <v>Yes</v>
       </c>
-      <c r="P275" t="str">
-        <v>32.25180835555556</v>
+      <c r="P275">
+        <v>32.2537229</v>
       </c>
       <c r="Q275">
-        <v>-64.8333210666666</v>
+        <v>-64.8351824</v>
       </c>
     </row>
     <row r="276" xml:space="preserve">
@@ -15605,10 +15605,10 @@
         <v>Yes</v>
       </c>
       <c r="P279">
-        <v>32.264353</v>
+        <v>32.263842</v>
       </c>
       <c r="Q279">
-        <v>-64.819995</v>
+        <v>-64.821897</v>
       </c>
     </row>
     <row r="280" xml:space="preserve">
@@ -16582,10 +16582,10 @@
         <v>Yes</v>
       </c>
       <c r="P297">
-        <v>32.304914</v>
+        <v>32.3056539905629</v>
       </c>
       <c r="Q297">
-        <v>-64.789226</v>
+        <v>-64.78817544197068</v>
       </c>
     </row>
     <row r="298" xml:space="preserve">
@@ -16746,10 +16746,10 @@
         <v>Yes</v>
       </c>
       <c r="P300">
-        <v>32.2808345</v>
+        <v>32.280388</v>
       </c>
       <c r="Q300">
-        <v>-64.7962048</v>
+        <v>-64.796549</v>
       </c>
     </row>
     <row r="301" xml:space="preserve">
@@ -17073,10 +17073,10 @@
         <v>Yes</v>
       </c>
       <c r="P306">
-        <v>32.3008855</v>
+        <v>32.3015127</v>
       </c>
       <c r="Q306">
-        <v>-64.864057</v>
+        <v>-64.8639537</v>
       </c>
     </row>
     <row r="307" xml:space="preserve">
@@ -17128,10 +17128,10 @@
         <v>Yes</v>
       </c>
       <c r="P307">
-        <v>32.298994</v>
+        <v>32.298722</v>
       </c>
       <c r="Q307">
-        <v>-64.804708</v>
+        <v>-64.805815</v>
       </c>
     </row>
     <row r="308" xml:space="preserve">
@@ -17290,10 +17290,10 @@
         <v>Yes</v>
       </c>
       <c r="P310">
-        <v>32.263842</v>
+        <v>32.2678602</v>
       </c>
       <c r="Q310">
-        <v>-64.821897</v>
+        <v>-64.8053367</v>
       </c>
     </row>
     <row r="311" xml:space="preserve">
@@ -17344,10 +17344,10 @@
         <v>Yes</v>
       </c>
       <c r="P311">
-        <v>32.2942895</v>
+        <v>32.2942916</v>
       </c>
       <c r="Q311">
-        <v>-64.8035103</v>
+        <v>-64.803488</v>
       </c>
     </row>
     <row r="312" xml:space="preserve">
@@ -17398,10 +17398,10 @@
         <v>Yes</v>
       </c>
       <c r="P312">
-        <v>32.275466</v>
+        <v>32.275437</v>
       </c>
       <c r="Q312">
-        <v>-64.792692</v>
+        <v>-64.7926468</v>
       </c>
     </row>
     <row r="313" xml:space="preserve">
@@ -17507,10 +17507,10 @@
         <v>Yes</v>
       </c>
       <c r="P314">
-        <v>32.293971</v>
+        <v>32.2941084</v>
       </c>
       <c r="Q314">
-        <v>-64.87229</v>
+        <v>-64.8725165</v>
       </c>
     </row>
     <row r="315" xml:space="preserve">
@@ -17887,10 +17887,10 @@
         <v>Yes</v>
       </c>
       <c r="P321">
-        <v>32.294439</v>
+        <v>32.294184</v>
       </c>
       <c r="Q321">
-        <v>-64.798828</v>
+        <v>-64.795714</v>
       </c>
     </row>
     <row r="322" xml:space="preserve">
@@ -18265,10 +18265,10 @@
         <v>Yes</v>
       </c>
       <c r="P328">
-        <v>32.293578</v>
+        <v>32.280726</v>
       </c>
       <c r="Q328">
-        <v>-64.758978</v>
+        <v>-64.776702</v>
       </c>
     </row>
     <row r="329" xml:space="preserve">
@@ -18319,10 +18319,10 @@
         <v>Yes</v>
       </c>
       <c r="P329">
-        <v>32.29394</v>
+        <v>32.293985</v>
       </c>
       <c r="Q329">
-        <v>-64.785606</v>
+        <v>-64.78753</v>
       </c>
     </row>
     <row r="330" xml:space="preserve">
@@ -18590,10 +18590,10 @@
         <v>Yes</v>
       </c>
       <c r="P334">
-        <v>32.2806</v>
+        <v>32.28278</v>
       </c>
       <c r="Q334">
-        <v>-64.875154</v>
+        <v>-64.873352</v>
       </c>
     </row>
     <row r="335" xml:space="preserve">
@@ -18861,10 +18861,10 @@
         <v>Yes</v>
       </c>
       <c r="P339">
-        <v>32.249952</v>
+        <v>32.2495852</v>
       </c>
       <c r="Q339">
-        <v>-64.833779</v>
+        <v>-64.8351136</v>
       </c>
     </row>
     <row r="340" xml:space="preserve">
@@ -19131,10 +19131,10 @@
         <v>Yes</v>
       </c>
       <c r="P344">
-        <v>32.259797</v>
+        <v>32.2593908</v>
       </c>
       <c r="Q344">
-        <v>-64.811346</v>
+        <v>-64.8108396</v>
       </c>
     </row>
     <row r="345" xml:space="preserve">
@@ -19293,10 +19293,10 @@
         <v>Yes</v>
       </c>
       <c r="P347">
-        <v>32.2690077</v>
+        <v>32.269771</v>
       </c>
       <c r="Q347">
-        <v>-64.7880542</v>
+        <v>-64.798931</v>
       </c>
     </row>
     <row r="348" xml:space="preserve">
@@ -19401,10 +19401,10 @@
         <v>Yes</v>
       </c>
       <c r="P349">
-        <v>32.3222735</v>
+        <v>32.336144</v>
       </c>
       <c r="Q349">
-        <v>-64.7286219</v>
+        <v>-64.705058</v>
       </c>
     </row>
     <row r="350" xml:space="preserve">
@@ -19509,10 +19509,10 @@
         <v>Yes</v>
       </c>
       <c r="P351">
-        <v>32.301725</v>
+        <v>32.28898</v>
       </c>
       <c r="Q351">
-        <v>-64.868145</v>
+        <v>-64.8743</v>
       </c>
     </row>
     <row r="352" xml:space="preserve">
@@ -19616,11 +19616,11 @@
       <c r="O353" t="str">
         <v>Yes</v>
       </c>
-      <c r="P353" t="str">
-        <v>32.291840433333334</v>
+      <c r="P353">
+        <v>32.2925521</v>
       </c>
       <c r="Q353">
-        <v>-64.7637586333333</v>
+        <v>-64.7578132</v>
       </c>
     </row>
     <row r="354" xml:space="preserve">
@@ -19835,10 +19835,10 @@
         <v>Yes</v>
       </c>
       <c r="P357">
-        <v>32.289049</v>
+        <v>32.2879876</v>
       </c>
       <c r="Q357">
-        <v>-64.773041</v>
+        <v>-64.7724496</v>
       </c>
     </row>
     <row r="358" xml:space="preserve">
@@ -20213,11 +20213,11 @@
       <c r="O364" t="str">
         <v>Yes</v>
       </c>
-      <c r="P364" t="str">
-        <v>32.291840433333334</v>
+      <c r="P364">
+        <v>32.288622</v>
       </c>
       <c r="Q364">
-        <v>-64.7637586333333</v>
+        <v>-64.7612006</v>
       </c>
     </row>
     <row r="365" xml:space="preserve">
@@ -20377,10 +20377,10 @@
         <v>Yes</v>
       </c>
       <c r="P367">
-        <v>32.303726</v>
+        <v>32.3036953</v>
       </c>
       <c r="Q367">
-        <v>-64.755791</v>
+        <v>-64.7558272</v>
       </c>
     </row>
     <row r="368" xml:space="preserve">
@@ -20431,10 +20431,10 @@
         <v>Yes</v>
       </c>
       <c r="P368">
-        <v>32.3315121</v>
+        <v>32.334999</v>
       </c>
       <c r="Q368">
-        <v>-64.7112575</v>
+        <v>-64.706698</v>
       </c>
     </row>
     <row r="369" xml:space="preserve">
@@ -20485,10 +20485,10 @@
         <v>Yes</v>
       </c>
       <c r="P369">
-        <v>32.261322</v>
+        <v>32.2615491</v>
       </c>
       <c r="Q369">
-        <v>-64.869343</v>
+        <v>-64.8701001</v>
       </c>
     </row>
     <row r="370" xml:space="preserve">
@@ -20593,10 +20593,10 @@
         <v>Yes</v>
       </c>
       <c r="P371">
-        <v>32.3209063</v>
+        <v>32.324886</v>
       </c>
       <c r="Q371">
-        <v>-64.7153341</v>
+        <v>-64.715552</v>
       </c>
     </row>
     <row r="372" xml:space="preserve">
@@ -20701,10 +20701,10 @@
         <v>Yes</v>
       </c>
       <c r="P373">
-        <v>32.276969</v>
+        <v>32.279847</v>
       </c>
       <c r="Q373">
-        <v>-64.800649</v>
+        <v>-64.79798</v>
       </c>
     </row>
     <row r="374" xml:space="preserve">
@@ -20755,10 +20755,10 @@
         <v>Yes</v>
       </c>
       <c r="P374">
-        <v>32.3733407</v>
+        <v>32.3665563</v>
       </c>
       <c r="Q374">
-        <v>-64.6977803</v>
+        <v>-64.7085898</v>
       </c>
     </row>
     <row r="375" xml:space="preserve">
@@ -20809,10 +20809,10 @@
         <v>Yes</v>
       </c>
       <c r="P375">
-        <v>32.265839</v>
+        <v>32.2678602</v>
       </c>
       <c r="Q375">
-        <v>-64.829075</v>
+        <v>-64.8053367</v>
       </c>
     </row>
     <row r="376" xml:space="preserve">
@@ -21027,10 +21027,10 @@
         <v>Yes</v>
       </c>
       <c r="P379">
-        <v>32.268599</v>
+        <v>32.2689034</v>
       </c>
       <c r="Q379">
-        <v>-64.872374</v>
+        <v>-64.8730081</v>
       </c>
     </row>
     <row r="380" xml:space="preserve">
@@ -21135,10 +21135,10 @@
         <v>Yes</v>
       </c>
       <c r="P381">
-        <v>32.3131214</v>
+        <v>32.3183113</v>
       </c>
       <c r="Q381">
-        <v>-64.72813665</v>
+        <v>-64.7261038</v>
       </c>
     </row>
     <row r="382" xml:space="preserve">
@@ -21243,10 +21243,10 @@
         <v>Yes</v>
       </c>
       <c r="P383">
-        <v>32.3175347</v>
+        <v>32.3163615</v>
       </c>
       <c r="Q383">
-        <v>-64.7463399666666</v>
+        <v>-64.7462481</v>
       </c>
     </row>
     <row r="384" xml:space="preserve">
@@ -21297,10 +21297,10 @@
         <v>Yes</v>
       </c>
       <c r="P384">
-        <v>32.30365765</v>
+        <v>32.3052488</v>
       </c>
       <c r="Q384">
-        <v>-64.8067879</v>
+        <v>-64.8074867</v>
       </c>
     </row>
     <row r="385" xml:space="preserve">
@@ -21353,10 +21353,10 @@
         <v>Yes</v>
       </c>
       <c r="P385">
-        <v>32.296348</v>
+        <v>32.2961873</v>
       </c>
       <c r="Q385">
-        <v>-64.801174</v>
+        <v>-64.801126</v>
       </c>
     </row>
     <row r="386" xml:space="preserve">
@@ -21627,10 +21627,10 @@
         <v>Yes</v>
       </c>
       <c r="P390">
-        <v>32.302134</v>
+        <v>32.302835</v>
       </c>
       <c r="Q390">
-        <v>-64.81198</v>
+        <v>-64.812383</v>
       </c>
     </row>
     <row r="391" xml:space="preserve">
@@ -21789,10 +21789,10 @@
         <v>Yes</v>
       </c>
       <c r="P393">
-        <v>32.294307</v>
+        <v>32.2941853</v>
       </c>
       <c r="Q393">
-        <v>-64.774715</v>
+        <v>-64.7736257</v>
       </c>
     </row>
     <row r="394" xml:space="preserve">
@@ -21897,10 +21897,10 @@
         <v>Yes</v>
       </c>
       <c r="P395">
-        <v>32.294235</v>
+        <v>32.2940416</v>
       </c>
       <c r="Q395">
-        <v>-64.765527</v>
+        <v>-64.7640316</v>
       </c>
     </row>
     <row r="396" xml:space="preserve">
@@ -22061,10 +22061,10 @@
         <v>Yes</v>
       </c>
       <c r="P398">
-        <v>32.319315</v>
+        <v>32.3193636</v>
       </c>
       <c r="Q398">
-        <v>-64.723982</v>
+        <v>-64.7234988</v>
       </c>
     </row>
     <row r="399" xml:space="preserve">
@@ -22341,10 +22341,10 @@
         <v>Yes</v>
       </c>
       <c r="P403">
-        <v>32.269346975</v>
+        <v>32.2678602</v>
       </c>
       <c r="Q403">
-        <v>-64.807804025</v>
+        <v>-64.8053367</v>
       </c>
     </row>
     <row r="404" xml:space="preserve">
@@ -22719,10 +22719,10 @@
         <v>Yes</v>
       </c>
       <c r="P410">
-        <v>32.269771</v>
+        <v>32.271113</v>
       </c>
       <c r="Q410">
-        <v>-64.798931</v>
+        <v>-64.799826</v>
       </c>
     </row>
     <row r="411" xml:space="preserve">
@@ -22881,10 +22881,10 @@
         <v>Yes</v>
       </c>
       <c r="P413">
-        <v>32.285071</v>
+        <v>32.2836747</v>
       </c>
       <c r="Q413">
-        <v>-64.771347</v>
+        <v>-64.7709035</v>
       </c>
     </row>
     <row r="414" xml:space="preserve">
@@ -22989,10 +22989,10 @@
         <v>Yes</v>
       </c>
       <c r="P415">
-        <v>32.269334</v>
+        <v>32.2692295</v>
       </c>
       <c r="Q415">
-        <v>-64.792456</v>
+        <v>-64.7922798</v>
       </c>
     </row>
     <row r="416" xml:space="preserve">
@@ -23259,10 +23259,10 @@
         <v>Yes</v>
       </c>
       <c r="P420">
-        <v>32.304807</v>
+        <v>32.3050604</v>
       </c>
       <c r="Q420">
-        <v>-64.791546</v>
+        <v>-64.7911956</v>
       </c>
     </row>
     <row r="421" xml:space="preserve">
@@ -23367,10 +23367,10 @@
         <v>Yes</v>
       </c>
       <c r="P422">
-        <v>32.3209063</v>
+        <v>32.324435</v>
       </c>
       <c r="Q422">
-        <v>-64.7153341</v>
+        <v>-64.715038</v>
       </c>
     </row>
     <row r="423" xml:space="preserve">
@@ -23421,10 +23421,10 @@
         <v>Yes</v>
       </c>
       <c r="P423">
-        <v>32.319887</v>
+        <v>32.320226</v>
       </c>
       <c r="Q423">
-        <v>-64.739033</v>
+        <v>-64.7395011</v>
       </c>
     </row>
     <row r="424" xml:space="preserve">
@@ -23475,10 +23475,10 @@
         <v>Yes</v>
       </c>
       <c r="P424">
-        <v>32.280359</v>
+        <v>32.2796943</v>
       </c>
       <c r="Q424">
-        <v>-64.791405</v>
+        <v>-64.78902</v>
       </c>
     </row>
     <row r="425" xml:space="preserve">
@@ -23529,10 +23529,10 @@
         <v>Yes</v>
       </c>
       <c r="P425">
-        <v>32.30409</v>
+        <v>32.303055</v>
       </c>
       <c r="Q425">
-        <v>-64.798245</v>
+        <v>-64.797524</v>
       </c>
     </row>
     <row r="426" xml:space="preserve">
@@ -23636,11 +23636,11 @@
       <c r="O427" t="str">
         <v>Yes</v>
       </c>
-      <c r="P427" t="str">
-        <v>32.29370414931507</v>
+      <c r="P427">
+        <v>32.3008022</v>
       </c>
       <c r="Q427">
-        <v>-64.8038436136986</v>
+        <v>-64.7915912</v>
       </c>
     </row>
     <row r="428" xml:space="preserve">
@@ -23746,10 +23746,10 @@
         <v>Yes</v>
       </c>
       <c r="P429">
-        <v>32.2971141</v>
+        <v>32.2971204</v>
       </c>
       <c r="Q429">
-        <v>-64.7849691</v>
+        <v>-64.7849699</v>
       </c>
     </row>
     <row r="430" xml:space="preserve">
@@ -23800,10 +23800,10 @@
         <v>Yes</v>
       </c>
       <c r="P430">
-        <v>32.313969</v>
+        <v>32.3126921</v>
       </c>
       <c r="Q430">
-        <v>-64.734886</v>
+        <v>-64.7366104</v>
       </c>
     </row>
     <row r="431" xml:space="preserve">
@@ -23962,10 +23962,10 @@
         <v>Yes</v>
       </c>
       <c r="P433">
-        <v>32.296967</v>
+        <v>32.291726</v>
       </c>
       <c r="Q433">
-        <v>-64.79383</v>
+        <v>-64.791811</v>
       </c>
     </row>
     <row r="434" xml:space="preserve">
@@ -24016,10 +24016,10 @@
         <v>Yes</v>
       </c>
       <c r="P434">
-        <v>32.305303</v>
+        <v>32.3042233</v>
       </c>
       <c r="Q434">
-        <v>-64.737992</v>
+        <v>-64.738753</v>
       </c>
     </row>
     <row r="435" xml:space="preserve">
@@ -24235,10 +24235,10 @@
         <v>Yes</v>
       </c>
       <c r="P438">
-        <v>32.2927803</v>
+        <v>32.294539</v>
       </c>
       <c r="Q438">
-        <v>-64.872825</v>
+        <v>-64.869691</v>
       </c>
     </row>
     <row r="439" xml:space="preserve">
@@ -24505,10 +24505,10 @@
         <v>Yes</v>
       </c>
       <c r="P443">
-        <v>32.304396</v>
+        <v>32.3043467</v>
       </c>
       <c r="Q443">
-        <v>-64.815577</v>
+        <v>-64.8160778</v>
       </c>
     </row>
     <row r="444" xml:space="preserve">
@@ -24613,10 +24613,10 @@
         <v>Yes</v>
       </c>
       <c r="P445">
-        <v>32.301666</v>
+        <v>32.300753</v>
       </c>
       <c r="Q445">
-        <v>-64.866106</v>
+        <v>-64.867409</v>
       </c>
     </row>
     <row r="446" xml:space="preserve">
@@ -24775,10 +24775,10 @@
         <v>Yes</v>
       </c>
       <c r="P448">
-        <v>32.304179</v>
+        <v>32.3002368</v>
       </c>
       <c r="Q448">
-        <v>-64.752882</v>
+        <v>-64.74604</v>
       </c>
     </row>
     <row r="449" xml:space="preserve">
@@ -24993,10 +24993,10 @@
         <v>Yes</v>
       </c>
       <c r="P452">
-        <v>32.303834</v>
+        <v>32.3022975</v>
       </c>
       <c r="Q452">
-        <v>-64.753626</v>
+        <v>-64.7524478</v>
       </c>
     </row>
     <row r="453" xml:space="preserve">
@@ -25102,10 +25102,10 @@
         <v>Yes</v>
       </c>
       <c r="P454">
-        <v>32.2640995</v>
+        <v>32.264353</v>
       </c>
       <c r="Q454">
-        <v>-64.8197959</v>
+        <v>-64.819995</v>
       </c>
     </row>
     <row r="455" xml:space="preserve">
@@ -25211,10 +25211,10 @@
         <v>Yes</v>
       </c>
       <c r="P456">
-        <v>32.312149</v>
+        <v>32.3131214</v>
       </c>
       <c r="Q456">
-        <v>-64.7327815</v>
+        <v>-64.72813665</v>
       </c>
     </row>
     <row r="457" xml:space="preserve">
@@ -25265,10 +25265,10 @@
         <v>Yes</v>
       </c>
       <c r="P457">
-        <v>32.3261835</v>
+        <v>32.325474</v>
       </c>
       <c r="Q457">
-        <v>-64.7147658</v>
+        <v>-64.715429</v>
       </c>
     </row>
     <row r="458" xml:space="preserve">
@@ -25319,10 +25319,10 @@
         <v>Yes</v>
       </c>
       <c r="P458">
-        <v>32.3353981</v>
+        <v>32.3354143</v>
       </c>
       <c r="Q458">
-        <v>-64.7335381</v>
+        <v>-64.7322707</v>
       </c>
     </row>
     <row r="459" xml:space="preserve">
@@ -25373,10 +25373,10 @@
         <v>Yes</v>
       </c>
       <c r="P459">
-        <v>32.3134028</v>
+        <v>32.312807</v>
       </c>
       <c r="Q459">
-        <v>-64.7534065</v>
+        <v>-64.752368</v>
       </c>
     </row>
     <row r="460" xml:space="preserve">
@@ -25427,10 +25427,10 @@
         <v>Yes</v>
       </c>
       <c r="P460">
-        <v>32.2868308</v>
+        <v>32.286988</v>
       </c>
       <c r="Q460">
-        <v>-64.7798414</v>
+        <v>-64.780185</v>
       </c>
     </row>
     <row r="461" xml:space="preserve">
@@ -25481,10 +25481,10 @@
         <v>Yes</v>
       </c>
       <c r="P461">
-        <v>32.2548832</v>
+        <v>32.254039</v>
       </c>
       <c r="Q461">
-        <v>-64.8406697</v>
+        <v>-64.84694</v>
       </c>
     </row>
     <row r="462" xml:space="preserve">
@@ -25535,10 +25535,10 @@
         <v>Yes</v>
       </c>
       <c r="P462">
-        <v>32.2917742</v>
+        <v>32.290606</v>
       </c>
       <c r="Q462">
-        <v>-64.7728753</v>
+        <v>-64.773248</v>
       </c>
     </row>
     <row r="463" xml:space="preserve">
@@ -25589,10 +25589,10 @@
         <v>Yes</v>
       </c>
       <c r="P463">
-        <v>32.3181993</v>
+        <v>32.317988</v>
       </c>
       <c r="Q463">
-        <v>-64.7457751</v>
+        <v>-64.745986</v>
       </c>
     </row>
     <row r="464" xml:space="preserve">
@@ -25697,10 +25697,10 @@
         <v>Yes</v>
       </c>
       <c r="P465">
-        <v>32.2794658</v>
+        <v>32.279516</v>
       </c>
       <c r="Q465">
-        <v>-64.7883467</v>
+        <v>-64.788076</v>
       </c>
     </row>
     <row r="466" xml:space="preserve">
@@ -25805,10 +25805,10 @@
         <v>Yes</v>
       </c>
       <c r="P467">
-        <v>32.3054803</v>
+        <v>32.306043</v>
       </c>
       <c r="Q467">
-        <v>-64.7521967</v>
+        <v>-64.752237</v>
       </c>
     </row>
     <row r="468" xml:space="preserve">
@@ -25859,10 +25859,10 @@
         <v>Yes</v>
       </c>
       <c r="P468">
-        <v>32.3164596</v>
+        <v>32.316798</v>
       </c>
       <c r="Q468">
-        <v>-64.7199353</v>
+        <v>-64.719565</v>
       </c>
     </row>
     <row r="469" xml:space="preserve">
@@ -25913,10 +25913,10 @@
         <v>Yes</v>
       </c>
       <c r="P469">
-        <v>32.2810717</v>
+        <v>32.2699725</v>
       </c>
       <c r="Q469">
-        <v>-64.7756122</v>
+        <v>-64.7868268</v>
       </c>
     </row>
     <row r="470" xml:space="preserve">
@@ -25967,10 +25967,10 @@
         <v>Yes</v>
       </c>
       <c r="P470">
-        <v>32.3191473</v>
+        <v>32.319556</v>
       </c>
       <c r="Q470">
-        <v>-64.720468</v>
+        <v>-64.720549</v>
       </c>
     </row>
     <row r="471" xml:space="preserve">
@@ -26021,10 +26021,10 @@
         <v>Yes</v>
       </c>
       <c r="P471">
-        <v>32.3066685</v>
+        <v>32.3131214</v>
       </c>
       <c r="Q471">
-        <v>-64.7397557</v>
+        <v>-64.72813665</v>
       </c>
     </row>
     <row r="472" xml:space="preserve">
@@ -26075,10 +26075,10 @@
         <v>Yes</v>
       </c>
       <c r="P472">
-        <v>32.3691168</v>
+        <v>32.369247</v>
       </c>
       <c r="Q472">
-        <v>-64.6659185</v>
+        <v>-64.66457</v>
       </c>
     </row>
     <row r="473" xml:space="preserve">
@@ -26129,10 +26129,10 @@
         <v>Yes</v>
       </c>
       <c r="P473">
-        <v>32.2485197</v>
+        <v>32.248954</v>
       </c>
       <c r="Q473">
-        <v>-64.8392014</v>
+        <v>-64.844145</v>
       </c>
     </row>
     <row r="474" xml:space="preserve">
@@ -26183,10 +26183,10 @@
         <v>Yes</v>
       </c>
       <c r="P474">
-        <v>32.2528267</v>
+        <v>32.252656</v>
       </c>
       <c r="Q474">
-        <v>-64.8345101</v>
+        <v>-64.836254</v>
       </c>
     </row>
     <row r="475" xml:space="preserve">
@@ -26237,10 +26237,10 @@
         <v>Yes</v>
       </c>
       <c r="P475">
-        <v>32.3181969</v>
+        <v>32.3193995</v>
       </c>
       <c r="Q475">
-        <v>-64.7248279</v>
+        <v>-64.7255581</v>
       </c>
     </row>
     <row r="476" xml:space="preserve">
@@ -26291,10 +26291,10 @@
         <v>Yes</v>
       </c>
       <c r="P476">
-        <v>32.320632</v>
+        <v>32.31643</v>
       </c>
       <c r="Q476">
-        <v>-64.72602</v>
+        <v>-64.720511</v>
       </c>
     </row>
     <row r="477" xml:space="preserve">
@@ -26345,10 +26345,10 @@
         <v>Yes</v>
       </c>
       <c r="P477">
-        <v>32.28383</v>
+        <v>32.284045</v>
       </c>
       <c r="Q477">
-        <v>-64.7866553</v>
+        <v>-64.783545</v>
       </c>
     </row>
     <row r="478" xml:space="preserve">
@@ -26399,10 +26399,10 @@
         <v>Yes</v>
       </c>
       <c r="P478">
-        <v>32.2691111</v>
+        <v>32.269209</v>
       </c>
       <c r="Q478">
-        <v>-64.8099144</v>
+        <v>-64.810727</v>
       </c>
     </row>
     <row r="479" xml:space="preserve">
@@ -26453,10 +26453,10 @@
         <v>Yes</v>
       </c>
       <c r="P479">
-        <v>32.3661607</v>
+        <v>32.3661611</v>
       </c>
       <c r="Q479">
-        <v>-64.6535595</v>
+        <v>-64.653535</v>
       </c>
     </row>
     <row r="480" xml:space="preserve">
@@ -26509,10 +26509,10 @@
         <v>Yes</v>
       </c>
       <c r="P480">
-        <v>32.3112462</v>
+        <v>32.311464</v>
       </c>
       <c r="Q480">
-        <v>-64.7451129</v>
+        <v>-64.745214</v>
       </c>
     </row>
     <row r="481" xml:space="preserve">
@@ -26563,10 +26563,10 @@
         <v>Yes</v>
       </c>
       <c r="P481">
-        <v>32.2774325</v>
+        <v>32.277845</v>
       </c>
       <c r="Q481">
-        <v>-64.7978015</v>
+        <v>-64.798117</v>
       </c>
     </row>
     <row r="482" xml:space="preserve">
@@ -26672,10 +26672,10 @@
         <v>Yes</v>
       </c>
       <c r="P483">
-        <v>32.2572071</v>
+        <v>32.257463</v>
       </c>
       <c r="Q483">
-        <v>-64.8260611</v>
+        <v>-64.827027</v>
       </c>
     </row>
     <row r="484" xml:space="preserve">
@@ -26726,10 +26726,10 @@
         <v>Yes</v>
       </c>
       <c r="P484">
-        <v>32.2786252</v>
+        <v>32.279867</v>
       </c>
       <c r="Q484">
-        <v>-64.7725157</v>
+        <v>-64.773622</v>
       </c>
     </row>
     <row r="485" xml:space="preserve">
@@ -26780,10 +26780,10 @@
         <v>Yes</v>
       </c>
       <c r="P485">
-        <v>32.2708999</v>
+        <v>32.27150525</v>
       </c>
       <c r="Q485">
-        <v>-64.8054885</v>
+        <v>-64.805102125</v>
       </c>
     </row>
     <row r="486" xml:space="preserve">
@@ -26835,10 +26835,10 @@
         <v>Yes</v>
       </c>
       <c r="P486">
-        <v>32.2524857</v>
+        <v>32.251302</v>
       </c>
       <c r="Q486">
-        <v>-64.8625334</v>
+        <v>-64.863728</v>
       </c>
     </row>
     <row r="487" xml:space="preserve">
@@ -26889,10 +26889,10 @@
         <v>Yes</v>
       </c>
       <c r="P487">
-        <v>32.3109093</v>
+        <v>32.310041</v>
       </c>
       <c r="Q487">
-        <v>-64.7392549</v>
+        <v>-64.739027</v>
       </c>
     </row>
     <row r="488" xml:space="preserve">
@@ -26943,10 +26943,10 @@
         <v>Yes</v>
       </c>
       <c r="P488">
-        <v>32.2795285</v>
+        <v>32.280109</v>
       </c>
       <c r="Q488">
-        <v>-64.7955655</v>
+        <v>-64.795768</v>
       </c>
     </row>
     <row r="489" xml:space="preserve">
@@ -27001,10 +27001,10 @@
         <v>Yes</v>
       </c>
       <c r="P489">
-        <v>32.3778255</v>
+        <v>32.3778111</v>
       </c>
       <c r="Q489">
-        <v>-64.6851287</v>
+        <v>-64.6851087</v>
       </c>
     </row>
     <row r="490" xml:space="preserve">
@@ -27055,10 +27055,10 @@
         <v>Yes</v>
       </c>
       <c r="P490">
-        <v>32.2530379</v>
+        <v>32.251219</v>
       </c>
       <c r="Q490">
-        <v>-64.8272622</v>
+        <v>-64.826426</v>
       </c>
     </row>
     <row r="491" xml:space="preserve">
@@ -27109,10 +27109,10 @@
         <v>Yes</v>
       </c>
       <c r="P491">
-        <v>32.2870569</v>
+        <v>32.287189</v>
       </c>
       <c r="Q491">
-        <v>-64.7648372</v>
+        <v>-64.764582</v>
       </c>
     </row>
     <row r="492" xml:space="preserve">
@@ -27165,10 +27165,10 @@
         <v>Yes</v>
       </c>
       <c r="P492">
-        <v>32.3094792</v>
+        <v>32.309941</v>
       </c>
       <c r="Q492">
-        <v>-64.7362732</v>
+        <v>-64.736715</v>
       </c>
     </row>
     <row r="493" xml:space="preserve">
@@ -27219,10 +27219,10 @@
         <v>Yes</v>
       </c>
       <c r="P493">
-        <v>32.2947262</v>
+        <v>32.294973</v>
       </c>
       <c r="Q493">
-        <v>-64.7742435</v>
+        <v>-64.774144</v>
       </c>
     </row>
     <row r="494" xml:space="preserve">
@@ -27273,10 +27273,10 @@
         <v>Yes</v>
       </c>
       <c r="P494">
-        <v>32.2670941</v>
+        <v>32.2675509</v>
       </c>
       <c r="Q494">
-        <v>-64.8276166</v>
+        <v>-64.8258986</v>
       </c>
     </row>
     <row r="495" xml:space="preserve">
@@ -27327,10 +27327,10 @@
         <v>Yes</v>
       </c>
       <c r="P495">
-        <v>32.2646449</v>
+        <v>32.2647901</v>
       </c>
       <c r="Q495">
-        <v>-64.8185802</v>
+        <v>-64.8186259</v>
       </c>
     </row>
     <row r="496" xml:space="preserve">
@@ -27382,10 +27382,10 @@
         <v>Yes</v>
       </c>
       <c r="P496">
-        <v>32.323059</v>
+        <v>32.328542</v>
       </c>
       <c r="Q496">
-        <v>-64.7144607</v>
+        <v>-64.714037</v>
       </c>
     </row>
     <row r="497" xml:space="preserve">
@@ -27436,10 +27436,10 @@
         <v>Yes</v>
       </c>
       <c r="P497">
-        <v>32.2935498</v>
+        <v>32.292103</v>
       </c>
       <c r="Q497">
-        <v>-64.7936659</v>
+        <v>-64.79373</v>
       </c>
     </row>
     <row r="498" xml:space="preserve">
@@ -27544,10 +27544,10 @@
         <v>Yes</v>
       </c>
       <c r="P499">
-        <v>32.2663861</v>
+        <v>32.266334</v>
       </c>
       <c r="Q499">
-        <v>-64.8168287</v>
+        <v>-64.816241</v>
       </c>
     </row>
     <row r="500" xml:space="preserve">
@@ -27598,10 +27598,10 @@
         <v>Yes</v>
       </c>
       <c r="P500">
-        <v>32.3003681</v>
+        <v>32.300356</v>
       </c>
       <c r="Q500">
-        <v>-64.8069823</v>
+        <v>-64.807231</v>
       </c>
     </row>
     <row r="501" xml:space="preserve">
@@ -27652,10 +27652,10 @@
         <v>Yes</v>
       </c>
       <c r="P501">
-        <v>32.2577915</v>
+        <v>32.258021</v>
       </c>
       <c r="Q501">
-        <v>-64.8646373</v>
+        <v>-64.86375</v>
       </c>
     </row>
     <row r="502" xml:space="preserve">
@@ -27706,10 +27706,10 @@
         <v>Yes</v>
       </c>
       <c r="P502">
-        <v>32.3261835</v>
+        <v>32.325188</v>
       </c>
       <c r="Q502">
-        <v>-64.7147658</v>
+        <v>-64.715632</v>
       </c>
     </row>
     <row r="503" xml:space="preserve">
@@ -27760,10 +27760,10 @@
         <v>Yes</v>
       </c>
       <c r="P503">
-        <v>32.2631567</v>
+        <v>32.26177</v>
       </c>
       <c r="Q503">
-        <v>-64.805297</v>
+        <v>-64.810261</v>
       </c>
     </row>
     <row r="504" xml:space="preserve">
@@ -27922,10 +27922,10 @@
         <v>Yes</v>
       </c>
       <c r="P506">
-        <v>32.2959973</v>
+        <v>32.2959924</v>
       </c>
       <c r="Q506">
-        <v>-64.7891365</v>
+        <v>-64.7891301</v>
       </c>
     </row>
     <row r="507" xml:space="preserve">
@@ -27976,10 +27976,10 @@
         <v>Yes</v>
       </c>
       <c r="P507">
-        <v>32.2927803</v>
+        <v>32.292965</v>
       </c>
       <c r="Q507">
-        <v>-64.872825</v>
+        <v>-64.873206</v>
       </c>
     </row>
     <row r="508" xml:space="preserve">
@@ -28084,10 +28084,10 @@
         <v>Yes</v>
       </c>
       <c r="P509">
-        <v>32.29295</v>
+        <v>32.2929406</v>
       </c>
       <c r="Q509">
-        <v>-64.8014446</v>
+        <v>-64.8014382</v>
       </c>
     </row>
     <row r="510" xml:space="preserve">
@@ -28138,10 +28138,10 @@
         <v>Yes</v>
       </c>
       <c r="P510">
-        <v>32.2485197</v>
+        <v>32.250391</v>
       </c>
       <c r="Q510">
-        <v>-64.8392014</v>
+        <v>-64.85057</v>
       </c>
     </row>
     <row r="511" xml:space="preserve">
@@ -28192,10 +28192,10 @@
         <v>Yes</v>
       </c>
       <c r="P511">
-        <v>32.3026094</v>
+        <v>32.302755</v>
       </c>
       <c r="Q511">
-        <v>-64.7913686</v>
+        <v>-64.791491</v>
       </c>
     </row>
     <row r="512" xml:space="preserve">
@@ -28246,10 +28246,10 @@
         <v>Yes</v>
       </c>
       <c r="P512">
-        <v>32.2641873</v>
+        <v>32.263759</v>
       </c>
       <c r="Q512">
-        <v>-64.8177186</v>
+        <v>-64.817458</v>
       </c>
     </row>
     <row r="513" xml:space="preserve">
@@ -28307,10 +28307,10 @@
         <v>Yes</v>
       </c>
       <c r="P513">
-        <v>32.2756986</v>
+        <v>32.274768</v>
       </c>
       <c r="Q513">
-        <v>-64.8014238</v>
+        <v>-64.801626</v>
       </c>
     </row>
     <row r="514" xml:space="preserve">
@@ -28415,10 +28415,10 @@
         <v>Yes</v>
       </c>
       <c r="P515">
-        <v>32.3151461</v>
+        <v>32.314425</v>
       </c>
       <c r="Q515">
-        <v>-64.7419163</v>
+        <v>-64.742002</v>
       </c>
     </row>
     <row r="516" xml:space="preserve">
@@ -28469,10 +28469,10 @@
         <v>Yes</v>
       </c>
       <c r="P516">
-        <v>32.314425</v>
+        <v>32.3183028</v>
       </c>
       <c r="Q516">
-        <v>-64.742002</v>
+        <v>-64.7387109</v>
       </c>
     </row>
     <row r="517" xml:space="preserve">
@@ -28523,10 +28523,10 @@
         <v>Yes</v>
       </c>
       <c r="P517">
-        <v>32.318284</v>
+        <v>32.3092928</v>
       </c>
       <c r="Q517">
-        <v>-64.740346</v>
+        <v>-64.7335728</v>
       </c>
     </row>
     <row r="518" xml:space="preserve">
@@ -28685,10 +28685,10 @@
         <v>Yes</v>
       </c>
       <c r="P520">
-        <v>32.2935498</v>
+        <v>32.295816</v>
       </c>
       <c r="Q520">
-        <v>-64.7936659</v>
+        <v>-64.794069</v>
       </c>
     </row>
     <row r="521" xml:space="preserve">
@@ -28796,10 +28796,10 @@
         <v>Yes</v>
       </c>
       <c r="P522">
-        <v>32.2774325</v>
+        <v>32.276808</v>
       </c>
       <c r="Q522">
-        <v>-64.7978015</v>
+        <v>-64.798074</v>
       </c>
     </row>
     <row r="523" xml:space="preserve">
@@ -28850,10 +28850,10 @@
         <v>Yes</v>
       </c>
       <c r="P523">
-        <v>32.277845</v>
+        <v>32.273333</v>
       </c>
       <c r="Q523">
-        <v>-64.798117</v>
+        <v>-64.806729</v>
       </c>
     </row>
     <row r="524" xml:space="preserve">
@@ -28904,10 +28904,10 @@
         <v>Yes</v>
       </c>
       <c r="P524">
-        <v>32.2764191</v>
+        <v>32.275318</v>
       </c>
       <c r="Q524">
-        <v>-64.8773217</v>
+        <v>-64.878373</v>
       </c>
     </row>
     <row r="525" xml:space="preserve">
@@ -29282,10 +29282,10 @@
         <v>Yes</v>
       </c>
       <c r="P531">
-        <v>32.3034207</v>
+        <v>32.303706</v>
       </c>
       <c r="Q531">
-        <v>-64.8049474</v>
+        <v>-64.805129</v>
       </c>
     </row>
     <row r="532" xml:space="preserve">
@@ -29336,10 +29336,10 @@
         <v>Yes</v>
       </c>
       <c r="P532">
-        <v>32.2972569</v>
+        <v>32.296993</v>
       </c>
       <c r="Q532">
-        <v>-64.7512587</v>
+        <v>-64.75129</v>
       </c>
     </row>
     <row r="533" xml:space="preserve">
@@ -29445,10 +29445,10 @@
         <v>Yes</v>
       </c>
       <c r="P534">
-        <v>32.272155</v>
+        <v>32.27254</v>
       </c>
       <c r="Q534">
-        <v>-64.7866886</v>
+        <v>-64.786562</v>
       </c>
     </row>
     <row r="535" xml:space="preserve">
@@ -29499,10 +29499,10 @@
         <v>Yes</v>
       </c>
       <c r="P535">
-        <v>32.299317</v>
+        <v>32.299257</v>
       </c>
       <c r="Q535">
-        <v>-64.7567287</v>
+        <v>-64.755618</v>
       </c>
     </row>
     <row r="536" xml:space="preserve">
@@ -29662,10 +29662,10 @@
         <v>Yes</v>
       </c>
       <c r="P538">
-        <v>32.3355446</v>
+        <v>32.336613</v>
       </c>
       <c r="Q538">
-        <v>-64.7395971</v>
+        <v>-64.739729</v>
       </c>
     </row>
     <row r="539" xml:space="preserve">
@@ -29716,10 +29716,10 @@
         <v>Yes</v>
       </c>
       <c r="P539">
-        <v>32.2808345</v>
+        <v>32.269312</v>
       </c>
       <c r="Q539">
-        <v>-64.7962048</v>
+        <v>-64.816535</v>
       </c>
     </row>
     <row r="540" xml:space="preserve">
@@ -29771,10 +29771,10 @@
         <v>Yes</v>
       </c>
       <c r="P540">
-        <v>32.3828525</v>
+        <v>32.382931</v>
       </c>
       <c r="Q540">
-        <v>-64.6756054</v>
+        <v>-64.67565</v>
       </c>
     </row>
     <row r="541" xml:space="preserve">
@@ -29879,10 +29879,10 @@
         <v>Yes</v>
       </c>
       <c r="P542">
-        <v>32.2806594</v>
+        <v>32.280962</v>
       </c>
       <c r="Q542">
-        <v>-64.7776944</v>
+        <v>-64.777781</v>
       </c>
     </row>
     <row r="543" xml:space="preserve">
@@ -29933,10 +29933,10 @@
         <v>Yes</v>
       </c>
       <c r="P543">
-        <v>32.264039</v>
+        <v>32.264557</v>
       </c>
       <c r="Q543">
-        <v>-64.8083577</v>
+        <v>-64.808841</v>
       </c>
     </row>
     <row r="544" xml:space="preserve">
@@ -29989,10 +29989,10 @@
         <v>Yes</v>
       </c>
       <c r="P544">
-        <v>32.3142004</v>
+        <v>32.314128</v>
       </c>
       <c r="Q544">
-        <v>-64.745519</v>
+        <v>-64.745546</v>
       </c>
     </row>
     <row r="545" xml:space="preserve">
@@ -30043,10 +30043,10 @@
         <v>Yes</v>
       </c>
       <c r="P545">
-        <v>32.2986532</v>
+        <v>32.299549</v>
       </c>
       <c r="Q545">
-        <v>-64.8030275</v>
+        <v>-64.802894</v>
       </c>
     </row>
     <row r="546" xml:space="preserve">
@@ -30097,10 +30097,10 @@
         <v>Yes</v>
       </c>
       <c r="P546">
-        <v>32.299549</v>
+        <v>32.296195</v>
       </c>
       <c r="Q546">
-        <v>-64.802894</v>
+        <v>-64.799507</v>
       </c>
     </row>
     <row r="547" xml:space="preserve">
@@ -30151,10 +30151,10 @@
         <v>Yes</v>
       </c>
       <c r="P547">
-        <v>32.2971245</v>
+        <v>32.297671</v>
       </c>
       <c r="Q547">
-        <v>-64.7863334</v>
+        <v>-64.785587</v>
       </c>
     </row>
     <row r="548" xml:space="preserve">
@@ -30205,10 +30205,10 @@
         <v>Yes</v>
       </c>
       <c r="P548">
-        <v>32.28505</v>
+        <v>32.286772</v>
       </c>
       <c r="Q548">
-        <v>-64.76539</v>
+        <v>-64.766868</v>
       </c>
     </row>
     <row r="549" xml:space="preserve">
@@ -30259,10 +30259,10 @@
         <v>Yes</v>
       </c>
       <c r="P549">
-        <v>32.2935435</v>
+        <v>32.2930967</v>
       </c>
       <c r="Q549">
-        <v>-64.8054161</v>
+        <v>-64.8055015</v>
       </c>
     </row>
     <row r="550" xml:space="preserve">
@@ -30313,10 +30313,10 @@
         <v>Yes</v>
       </c>
       <c r="P550">
-        <v>32.2899995</v>
+        <v>32.290426</v>
       </c>
       <c r="Q550">
-        <v>-64.7716785</v>
+        <v>-64.772063</v>
       </c>
     </row>
     <row r="551" xml:space="preserve">
@@ -30372,10 +30372,10 @@
         <v>Yes</v>
       </c>
       <c r="P551">
-        <v>32.3162755</v>
+        <v>32.316389</v>
       </c>
       <c r="Q551">
-        <v>-64.7185543</v>
+        <v>-64.718497</v>
       </c>
     </row>
     <row r="552" xml:space="preserve">
@@ -30426,10 +30426,10 @@
         <v>Yes</v>
       </c>
       <c r="P552">
-        <v>32.302786</v>
+        <v>32.302098</v>
       </c>
       <c r="Q552">
-        <v>-64.7605636</v>
+        <v>-64.761213</v>
       </c>
     </row>
     <row r="553" xml:space="preserve">
@@ -30760,10 +30760,10 @@
         <v>Yes</v>
       </c>
       <c r="P558">
-        <v>32.281139</v>
+        <v>32.2810336</v>
       </c>
       <c r="Q558">
-        <v>-64.7952834</v>
+        <v>-64.7948055</v>
       </c>
     </row>
     <row r="559" xml:space="preserve">
@@ -30873,10 +30873,10 @@
         <v>Yes</v>
       </c>
       <c r="P560">
-        <v>32.3010169</v>
+        <v>32.301149</v>
       </c>
       <c r="Q560">
-        <v>-64.7440821</v>
+        <v>-64.744688</v>
       </c>
     </row>
     <row r="561" xml:space="preserve">
@@ -30981,10 +30981,10 @@
         <v>Yes</v>
       </c>
       <c r="P562">
-        <v>32.3315121</v>
+        <v>32.329076</v>
       </c>
       <c r="Q562">
-        <v>-64.7112575</v>
+        <v>-64.712027</v>
       </c>
     </row>
     <row r="563" xml:space="preserve">
@@ -31035,10 +31035,10 @@
         <v>Yes</v>
       </c>
       <c r="P563">
-        <v>32.2526096</v>
+        <v>32.2529735</v>
       </c>
       <c r="Q563">
-        <v>-64.8390528</v>
+        <v>-64.8392026</v>
       </c>
     </row>
     <row r="564" xml:space="preserve">
@@ -31198,10 +31198,10 @@
         <v>Yes</v>
       </c>
       <c r="P566">
-        <v>32.3102938</v>
+        <v>32.310749</v>
       </c>
       <c r="Q566">
-        <v>-64.7423319</v>
+        <v>-64.743077</v>
       </c>
     </row>
     <row r="567" xml:space="preserve">
@@ -31307,10 +31307,10 @@
         <v>Yes</v>
       </c>
       <c r="P568">
-        <v>32.2654832</v>
+        <v>32.263911</v>
       </c>
       <c r="Q568">
-        <v>-64.8238379</v>
+        <v>-64.819931</v>
       </c>
     </row>
     <row r="569" xml:space="preserve">
@@ -31363,10 +31363,10 @@
         <v>Yes</v>
       </c>
       <c r="P569">
-        <v>32.2955586</v>
+        <v>32.296195</v>
       </c>
       <c r="Q569">
-        <v>-64.7993392</v>
+        <v>-64.799507</v>
       </c>
     </row>
     <row r="570" xml:space="preserve">
@@ -31417,10 +31417,10 @@
         <v>Yes</v>
       </c>
       <c r="P570">
-        <v>32.2509501</v>
+        <v>32.2511129</v>
       </c>
       <c r="Q570">
-        <v>-64.8525184</v>
+        <v>-64.8526628</v>
       </c>
     </row>
     <row r="571" xml:space="preserve">
@@ -31634,10 +31634,10 @@
         <v>Yes</v>
       </c>
       <c r="P574">
-        <v>32.2929044</v>
+        <v>32.291189</v>
       </c>
       <c r="Q574">
-        <v>-64.7660607</v>
+        <v>-64.766623</v>
       </c>
     </row>
     <row r="575" xml:space="preserve">
@@ -31688,10 +31688,10 @@
         <v>Yes</v>
       </c>
       <c r="P575">
-        <v>32.291779</v>
+        <v>32.283678</v>
       </c>
       <c r="Q575">
-        <v>-64.767231</v>
+        <v>-64.772568</v>
       </c>
     </row>
     <row r="576" xml:space="preserve">
@@ -31742,10 +31742,10 @@
         <v>Yes</v>
       </c>
       <c r="P576">
-        <v>32.3688103</v>
+        <v>32.368856</v>
       </c>
       <c r="Q576">
-        <v>-64.6701955</v>
+        <v>-64.669927</v>
       </c>
     </row>
     <row r="577" xml:space="preserve">
@@ -31851,10 +31851,10 @@
         <v>Yes</v>
       </c>
       <c r="P578">
-        <v>32.3053654</v>
+        <v>32.308037</v>
       </c>
       <c r="Q578">
-        <v>-64.7419944</v>
+        <v>-64.741357</v>
       </c>
     </row>
     <row r="579" xml:space="preserve">
@@ -31910,10 +31910,10 @@
         <v>Yes</v>
       </c>
       <c r="P579">
-        <v>32.2974108</v>
+        <v>32.297492</v>
       </c>
       <c r="Q579">
-        <v>-64.7689992</v>
+        <v>-64.768743</v>
       </c>
     </row>
     <row r="580" xml:space="preserve">
@@ -32027,10 +32027,10 @@
         <v>Yes</v>
       </c>
       <c r="P581">
-        <v>32.2936521</v>
+        <v>32.2936656</v>
       </c>
       <c r="Q581">
-        <v>-64.7730671</v>
+        <v>-64.772988</v>
       </c>
     </row>
     <row r="582" xml:space="preserve">
@@ -32088,10 +32088,10 @@
         <v>Yes</v>
       </c>
       <c r="P582">
-        <v>32.3796671</v>
+        <v>32.379659</v>
       </c>
       <c r="Q582">
-        <v>-64.6823322</v>
+        <v>-64.682414</v>
       </c>
     </row>
     <row r="583" xml:space="preserve">
@@ -32145,10 +32145,10 @@
         <v>Yes</v>
       </c>
       <c r="P583">
-        <v>32.3348651</v>
+        <v>32.334494</v>
       </c>
       <c r="Q583">
-        <v>-64.735571</v>
+        <v>-64.734906</v>
       </c>
     </row>
     <row r="584" xml:space="preserve">
@@ -32204,10 +32204,10 @@
         <v>Yes</v>
       </c>
       <c r="P584">
-        <v>32.3834092</v>
+        <v>32.3815884</v>
       </c>
       <c r="Q584">
-        <v>-64.668365</v>
+        <v>-64.6669631</v>
       </c>
     </row>
     <row r="585" xml:space="preserve">
@@ -32260,10 +32260,10 @@
         <v>Yes</v>
       </c>
       <c r="P585">
-        <v>32.2941512</v>
+        <v>32.294257</v>
       </c>
       <c r="Q585">
-        <v>-64.7950116</v>
+        <v>-64.794695</v>
       </c>
     </row>
     <row r="586" xml:space="preserve">
@@ -32315,10 +32315,10 @@
         <v>Yes</v>
       </c>
       <c r="P586">
-        <v>32.2749053</v>
+        <v>32.274754</v>
       </c>
       <c r="Q586">
-        <v>-64.7848039</v>
+        <v>-64.784855</v>
       </c>
     </row>
     <row r="587" xml:space="preserve">
@@ -32369,10 +32369,10 @@
         <v>Yes</v>
       </c>
       <c r="P587">
-        <v>32.3094792</v>
+        <v>32.310369</v>
       </c>
       <c r="Q587">
-        <v>-64.7362732</v>
+        <v>-64.736565</v>
       </c>
     </row>
     <row r="588" xml:space="preserve">
@@ -32427,10 +32427,10 @@
         <v>Yes</v>
       </c>
       <c r="P588">
-        <v>32.310369</v>
+        <v>32.314128</v>
       </c>
       <c r="Q588">
-        <v>-64.736565</v>
+        <v>-64.745546</v>
       </c>
     </row>
     <row r="589" xml:space="preserve">
@@ -32482,10 +32482,10 @@
         <v>Yes</v>
       </c>
       <c r="P589">
-        <v>32.2949592</v>
+        <v>32.294947</v>
       </c>
       <c r="Q589">
-        <v>-64.8041959</v>
+        <v>-64.8042311</v>
       </c>
     </row>
     <row r="590" xml:space="preserve">
@@ -32592,10 +32592,10 @@
         <v>Yes</v>
       </c>
       <c r="P591">
-        <v>32.2992642</v>
+        <v>32.299235</v>
       </c>
       <c r="Q591">
-        <v>-64.7820109</v>
+        <v>-64.781495</v>
       </c>
     </row>
     <row r="592" xml:space="preserve">
@@ -32707,10 +32707,10 @@
         <v>Yes</v>
       </c>
       <c r="P593">
-        <v>32.2591042</v>
+        <v>32.25866</v>
       </c>
       <c r="Q593">
-        <v>-64.82784</v>
+        <v>-64.827887</v>
       </c>
     </row>
     <row r="594" xml:space="preserve">
@@ -32763,10 +32763,10 @@
         <v>Yes</v>
       </c>
       <c r="P594">
-        <v>32.3304583</v>
+        <v>32.3304207</v>
       </c>
       <c r="Q594">
-        <v>-64.6999325</v>
+        <v>-64.6999353</v>
       </c>
     </row>
     <row r="595" xml:space="preserve">
@@ -33036,10 +33036,10 @@
         <v>Yes</v>
       </c>
       <c r="P599">
-        <v>32.2499162</v>
+        <v>32.249624</v>
       </c>
       <c r="Q599">
-        <v>-64.8305295</v>
+        <v>-64.830499</v>
       </c>
     </row>
     <row r="600" xml:space="preserve">
@@ -33147,10 +33147,10 @@
         <v>Yes</v>
       </c>
       <c r="P601">
-        <v>32.3003681</v>
+        <v>32.300798</v>
       </c>
       <c r="Q601">
-        <v>-64.8069823</v>
+        <v>-64.807608</v>
       </c>
     </row>
     <row r="602" xml:space="preserve">
@@ -33313,10 +33313,10 @@
         <v>Yes</v>
       </c>
       <c r="P604">
-        <v>32.3150082</v>
+        <v>32.315817</v>
       </c>
       <c r="Q604">
-        <v>-64.7306188</v>
+        <v>-64.730257</v>
       </c>
     </row>
     <row r="605" xml:space="preserve">
@@ -33369,10 +33369,10 @@
         <v>Yes</v>
       </c>
       <c r="P605">
-        <v>32.3036429</v>
+        <v>32.303933</v>
       </c>
       <c r="Q605">
-        <v>-64.7466159</v>
+        <v>-64.747048</v>
       </c>
     </row>
     <row r="606" xml:space="preserve">
@@ -33427,10 +33427,10 @@
         <v>Yes</v>
       </c>
       <c r="P606">
-        <v>32.2975434</v>
+        <v>32.297044</v>
       </c>
       <c r="Q606">
-        <v>-64.8640284</v>
+        <v>-64.863524</v>
       </c>
     </row>
     <row r="607" xml:space="preserve">
@@ -33542,10 +33542,10 @@
         <v>Yes</v>
       </c>
       <c r="P608">
-        <v>32.2747244</v>
+        <v>32.2776505</v>
       </c>
       <c r="Q608">
-        <v>-64.7859911</v>
+        <v>-64.781677</v>
       </c>
     </row>
     <row r="609" xml:space="preserve">
@@ -33599,10 +33599,10 @@
         <v>Yes</v>
       </c>
       <c r="P609">
-        <v>32.3031733</v>
+        <v>32.303992</v>
       </c>
       <c r="Q609">
-        <v>-64.7458741</v>
+        <v>-64.746425</v>
       </c>
     </row>
     <row r="610" xml:space="preserve">
@@ -33653,10 +33653,10 @@
         <v>Yes</v>
       </c>
       <c r="P610">
-        <v>32.272155</v>
+        <v>32.272609</v>
       </c>
       <c r="Q610">
-        <v>-64.7866886</v>
+        <v>-64.787361</v>
       </c>
     </row>
     <row r="611" xml:space="preserve">
@@ -33712,10 +33712,10 @@
         <v>Yes</v>
       </c>
       <c r="P611">
-        <v>32.2526759</v>
+        <v>32.252999</v>
       </c>
       <c r="Q611">
-        <v>-64.868319</v>
+        <v>-64.868366</v>
       </c>
     </row>
     <row r="612" xml:space="preserve">
@@ -33823,10 +33823,10 @@
         <v>Yes</v>
       </c>
       <c r="P613">
-        <v>32.3162755</v>
+        <v>32.316387</v>
       </c>
       <c r="Q613">
-        <v>-64.7185543</v>
+        <v>-64.718198</v>
       </c>
     </row>
     <row r="614" xml:space="preserve">
@@ -33877,10 +33877,10 @@
         <v>Yes</v>
       </c>
       <c r="P614">
-        <v>32.2500743</v>
+        <v>32.250024</v>
       </c>
       <c r="Q614">
-        <v>-64.8519534</v>
+        <v>-64.85148</v>
       </c>
     </row>
     <row r="615" xml:space="preserve">
@@ -33931,10 +33931,10 @@
         <v>Yes</v>
       </c>
       <c r="P615">
-        <v>32.2900621</v>
+        <v>32.290288</v>
       </c>
       <c r="Q615">
-        <v>-64.7690962</v>
+        <v>-64.769736</v>
       </c>
     </row>
     <row r="616" xml:space="preserve">
@@ -34040,10 +34040,10 @@
         <v>Yes</v>
       </c>
       <c r="P617">
-        <v>32.2678242</v>
+        <v>32.267747</v>
       </c>
       <c r="Q617">
-        <v>-64.8792317</v>
+        <v>-64.879456</v>
       </c>
     </row>
     <row r="618" xml:space="preserve">
@@ -34095,10 +34095,10 @@
         <v>Yes</v>
       </c>
       <c r="P618">
-        <v>32.28383</v>
+        <v>32.282617</v>
       </c>
       <c r="Q618">
-        <v>-64.7866553</v>
+        <v>-64.78968</v>
       </c>
     </row>
     <row r="619" xml:space="preserve">
@@ -34149,10 +34149,10 @@
         <v>Yes</v>
       </c>
       <c r="P619">
-        <v>32.2930502</v>
+        <v>32.293904</v>
       </c>
       <c r="Q619">
-        <v>-64.7860402</v>
+        <v>-64.786387</v>
       </c>
     </row>
     <row r="620" xml:space="preserve">
@@ -34260,10 +34260,10 @@
         <v>Yes</v>
       </c>
       <c r="P621">
-        <v>32.283819</v>
+        <v>32.2678602</v>
       </c>
       <c r="Q621">
-        <v>-64.80844</v>
+        <v>-64.8053367</v>
       </c>
     </row>
     <row r="622" xml:space="preserve">
@@ -34314,10 +34314,10 @@
         <v>Yes</v>
       </c>
       <c r="P622">
-        <v>32.3390095</v>
+        <v>32.337896</v>
       </c>
       <c r="Q622">
-        <v>-64.7001682</v>
+        <v>-64.701341</v>
       </c>
     </row>
     <row r="623" xml:space="preserve">
@@ -34423,10 +34423,10 @@
         <v>Yes</v>
       </c>
       <c r="P624">
-        <v>32.2923582</v>
+        <v>32.29234</v>
       </c>
       <c r="Q624">
-        <v>-64.785568</v>
+        <v>-64.785665</v>
       </c>
     </row>
     <row r="625" xml:space="preserve">
@@ -34477,10 +34477,10 @@
         <v>Yes</v>
       </c>
       <c r="P625">
-        <v>32.2936521</v>
+        <v>32.2936656</v>
       </c>
       <c r="Q625">
-        <v>-64.7730671</v>
+        <v>-64.772988</v>
       </c>
     </row>
     <row r="626" xml:space="preserve">
@@ -34531,10 +34531,10 @@
         <v>Yes</v>
       </c>
       <c r="P626">
-        <v>32.3819777</v>
+        <v>32.382026</v>
       </c>
       <c r="Q626">
-        <v>-64.6744969</v>
+        <v>-64.674536</v>
       </c>
     </row>
     <row r="627" xml:space="preserve">
@@ -34750,10 +34750,10 @@
         <v>Yes</v>
       </c>
       <c r="P630">
-        <v>32.3451982</v>
+        <v>32.344695</v>
       </c>
       <c r="Q630">
-        <v>-64.724489</v>
+        <v>-64.724579</v>
       </c>
     </row>
     <row r="631" xml:space="preserve">
@@ -34804,10 +34804,10 @@
         <v>Yes</v>
       </c>
       <c r="P631">
-        <v>32.2972569</v>
+        <v>32.296333</v>
       </c>
       <c r="Q631">
-        <v>-64.7512587</v>
+        <v>-64.75155</v>
       </c>
     </row>
     <row r="632" xml:space="preserve">
@@ -34859,10 +34859,10 @@
         <v>Yes</v>
       </c>
       <c r="P632">
-        <v>32.3761167</v>
+        <v>32.376398</v>
       </c>
       <c r="Q632">
-        <v>-64.6914793</v>
+        <v>-64.691503</v>
       </c>
     </row>
     <row r="633" xml:space="preserve">
@@ -34914,10 +34914,10 @@
         <v>Yes</v>
       </c>
       <c r="P633">
-        <v>32.2929693</v>
+        <v>32.2929526</v>
       </c>
       <c r="Q633">
-        <v>-64.8017899</v>
+        <v>-64.8017921</v>
       </c>
     </row>
     <row r="634" xml:space="preserve">
@@ -35026,10 +35026,10 @@
         <v>Yes</v>
       </c>
       <c r="P635">
-        <v>32.333877</v>
+        <v>32.33361</v>
       </c>
       <c r="Q635">
-        <v>-64.7408822</v>
+        <v>-64.740621</v>
       </c>
     </row>
     <row r="636" xml:space="preserve">
@@ -35080,10 +35080,10 @@
         <v>Yes</v>
       </c>
       <c r="P636">
-        <v>32.2877818</v>
+        <v>32.288179</v>
       </c>
       <c r="Q636">
-        <v>-64.7788884</v>
+        <v>-64.779644</v>
       </c>
     </row>
     <row r="637" xml:space="preserve">
@@ -35134,10 +35134,10 @@
         <v>Yes</v>
       </c>
       <c r="P637">
-        <v>32.2859375</v>
+        <v>32.282405</v>
       </c>
       <c r="Q637">
-        <v>-64.8713027</v>
+        <v>-64.871083</v>
       </c>
     </row>
     <row r="638" xml:space="preserve">
@@ -35243,10 +35243,10 @@
         <v>Yes</v>
       </c>
       <c r="P639">
-        <v>32.2550684</v>
+        <v>32.25534</v>
       </c>
       <c r="Q639">
-        <v>-64.8634519</v>
+        <v>-64.862894</v>
       </c>
     </row>
     <row r="640" xml:space="preserve">
@@ -35464,10 +35464,10 @@
         <v>Yes</v>
       </c>
       <c r="P643">
-        <v>32.261128</v>
+        <v>32.264039</v>
       </c>
       <c r="Q643">
-        <v>-64.813306</v>
+        <v>-64.8083577</v>
       </c>
     </row>
     <row r="644" xml:space="preserve">
@@ -35522,10 +35522,10 @@
         <v>Yes</v>
       </c>
       <c r="P644">
-        <v>32.2819691</v>
+        <v>32.281416</v>
       </c>
       <c r="Q644">
-        <v>-64.7719616</v>
+        <v>-64.771472</v>
       </c>
     </row>
     <row r="645" xml:space="preserve">
@@ -35586,10 +35586,10 @@
         <v>Yes</v>
       </c>
       <c r="P645">
-        <v>32.2936521</v>
+        <v>32.2936656</v>
       </c>
       <c r="Q645">
-        <v>-64.7730671</v>
+        <v>-64.772988</v>
       </c>
     </row>
     <row r="646" xml:space="preserve">
@@ -35641,10 +35641,10 @@
         <v>Yes</v>
       </c>
       <c r="P646">
-        <v>32.2819691</v>
+        <v>32.282667000000004</v>
       </c>
       <c r="Q646">
-        <v>-64.7719616</v>
+        <v>-64.771985</v>
       </c>
     </row>
     <row r="647" xml:space="preserve">
@@ -35695,10 +35695,10 @@
         <v>Yes</v>
       </c>
       <c r="P647">
-        <v>32.2732175</v>
+        <v>32.273322</v>
       </c>
       <c r="Q647">
-        <v>-64.8066971</v>
+        <v>-64.806901</v>
       </c>
     </row>
     <row r="648" xml:space="preserve">
@@ -35753,10 +35753,10 @@
         <v>Yes</v>
       </c>
       <c r="P648">
-        <v>32.273322</v>
+        <v>32.3008022</v>
       </c>
       <c r="Q648">
-        <v>-64.806901</v>
+        <v>-64.7915912</v>
       </c>
     </row>
     <row r="649" xml:space="preserve">
@@ -35867,10 +35867,10 @@
         <v>Yes</v>
       </c>
       <c r="P650">
-        <v>32.2526759</v>
+        <v>32.251885</v>
       </c>
       <c r="Q650">
-        <v>-64.868319</v>
+        <v>-64.867841</v>
       </c>
     </row>
     <row r="651" xml:space="preserve">
@@ -35980,10 +35980,10 @@
         <v>Yes</v>
       </c>
       <c r="P652">
-        <v>32.3516946</v>
+        <v>32.351726</v>
       </c>
       <c r="Q652">
-        <v>-64.7194111</v>
+        <v>-64.719244</v>
       </c>
     </row>
     <row r="653" xml:space="preserve">
@@ -36088,10 +36088,10 @@
         <v>Yes</v>
       </c>
       <c r="P654">
-        <v>32.299317</v>
+        <v>32.298704</v>
       </c>
       <c r="Q654">
-        <v>-64.7567287</v>
+        <v>-64.755451</v>
       </c>
     </row>
     <row r="655" xml:space="preserve">
@@ -36198,10 +36198,10 @@
         <v>Yes</v>
       </c>
       <c r="P656">
-        <v>32.2648045</v>
+        <v>32.264628</v>
       </c>
       <c r="Q656">
-        <v>-64.8058677</v>
+        <v>-64.806075</v>
       </c>
     </row>
     <row r="657" xml:space="preserve">
@@ -36306,10 +36306,10 @@
         <v>Yes</v>
       </c>
       <c r="P658">
-        <v>32.276808</v>
+        <v>32.2768464</v>
       </c>
       <c r="Q658">
-        <v>-64.798074</v>
+        <v>-64.7990126</v>
       </c>
     </row>
     <row r="659" xml:space="preserve">
@@ -36414,10 +36414,10 @@
         <v>Yes</v>
       </c>
       <c r="P660">
-        <v>32.2816087</v>
+        <v>32.281372</v>
       </c>
       <c r="Q660">
-        <v>-64.7782722</v>
+        <v>-64.777989</v>
       </c>
     </row>
     <row r="661" xml:space="preserve">
@@ -36470,10 +36470,10 @@
         <v>Yes</v>
       </c>
       <c r="P661">
-        <v>32.2929044</v>
+        <v>32.289433</v>
       </c>
       <c r="Q661">
-        <v>-64.7660607</v>
+        <v>-64.764698</v>
       </c>
     </row>
     <row r="662" xml:space="preserve">
@@ -36689,10 +36689,10 @@
         <v>Yes</v>
       </c>
       <c r="P665">
-        <v>32.3109093</v>
+        <v>32.310245</v>
       </c>
       <c r="Q665">
-        <v>-64.7392549</v>
+        <v>-64.738139</v>
       </c>
     </row>
     <row r="666" xml:space="preserve">
@@ -36805,10 +36805,10 @@
         <v>Yes</v>
       </c>
       <c r="P667">
-        <v>32.2931564</v>
+        <v>32.293206</v>
       </c>
       <c r="Q667">
-        <v>-64.7853842</v>
+        <v>-64.785407</v>
       </c>
     </row>
     <row r="668" xml:space="preserve">
@@ -36860,10 +36860,10 @@
         <v>Yes</v>
       </c>
       <c r="P668">
-        <v>32.293206</v>
+        <v>32.296842</v>
       </c>
       <c r="Q668">
-        <v>-64.785407</v>
+        <v>-64.793113</v>
       </c>
     </row>
     <row r="669" xml:space="preserve">
@@ -36915,10 +36915,10 @@
         <v>Yes</v>
       </c>
       <c r="P669">
-        <v>32.3041465</v>
+        <v>32.300608</v>
       </c>
       <c r="Q669">
-        <v>-64.7529387</v>
+        <v>-64.750419</v>
       </c>
     </row>
     <row r="670" xml:space="preserve">
@@ -37024,10 +37024,10 @@
         <v>Yes</v>
       </c>
       <c r="P671">
-        <v>32.32059</v>
+        <v>32.320723</v>
       </c>
       <c r="Q671">
-        <v>-64.7293269</v>
+        <v>-64.729884</v>
       </c>
     </row>
     <row r="672" xml:space="preserve">
@@ -37078,10 +37078,10 @@
         <v>Yes</v>
       </c>
       <c r="P672">
-        <v>32.320723</v>
+        <v>32.3161713</v>
       </c>
       <c r="Q672">
-        <v>-64.729884</v>
+        <v>-64.7224279</v>
       </c>
     </row>
     <row r="673" xml:space="preserve">
@@ -37186,10 +37186,10 @@
         <v>Yes</v>
       </c>
       <c r="P674">
-        <v>32.2988213</v>
+        <v>32.29855</v>
       </c>
       <c r="Q674">
-        <v>-64.7967052</v>
+        <v>-64.795771</v>
       </c>
     </row>
     <row r="675" xml:space="preserve">
@@ -37241,10 +37241,10 @@
         <v>Yes</v>
       </c>
       <c r="P675">
-        <v>32.3010169</v>
+        <v>32.301297</v>
       </c>
       <c r="Q675">
-        <v>-64.7440821</v>
+        <v>-64.743375</v>
       </c>
     </row>
     <row r="676" xml:space="preserve">
@@ -37301,10 +37301,10 @@
         <v>Yes</v>
       </c>
       <c r="P676">
-        <v>32.2560216</v>
+        <v>32.25617</v>
       </c>
       <c r="Q676">
-        <v>-64.8643495</v>
+        <v>-64.865239</v>
       </c>
     </row>
     <row r="677" xml:space="preserve">
@@ -37356,10 +37356,10 @@
         <v>Yes</v>
       </c>
       <c r="P677">
-        <v>32.2990511</v>
+        <v>32.299117</v>
       </c>
       <c r="Q677">
-        <v>-64.8000235</v>
+        <v>-64.799605</v>
       </c>
     </row>
     <row r="678" xml:space="preserve">
@@ -37410,10 +37410,10 @@
         <v>Yes</v>
       </c>
       <c r="P678">
-        <v>32.2657219</v>
+        <v>32.265453</v>
       </c>
       <c r="Q678">
-        <v>-64.800233</v>
+        <v>-64.800223</v>
       </c>
     </row>
     <row r="679" xml:space="preserve">
@@ -37522,10 +37522,10 @@
         <v>Yes</v>
       </c>
       <c r="P680">
-        <v>32.2931564</v>
+        <v>32.293206</v>
       </c>
       <c r="Q680">
-        <v>-64.7853842</v>
+        <v>-64.785407</v>
       </c>
     </row>
     <row r="681" xml:space="preserve">
@@ -37581,10 +37581,10 @@
         <v>Yes</v>
       </c>
       <c r="P681">
-        <v>32.3137553</v>
+        <v>32.313466</v>
       </c>
       <c r="Q681">
-        <v>-64.7334573</v>
+        <v>-64.733358</v>
       </c>
     </row>
     <row r="682" xml:space="preserve">
@@ -37635,10 +37635,10 @@
         <v>Yes</v>
       </c>
       <c r="P682">
-        <v>32.2923591</v>
+        <v>32.291976</v>
       </c>
       <c r="Q682">
-        <v>-64.770898</v>
+        <v>-64.77466</v>
       </c>
     </row>
     <row r="683" xml:space="preserve">
@@ -37754,10 +37754,10 @@
         <v>Yes</v>
       </c>
       <c r="P684">
-        <v>32.3282742</v>
+        <v>32.327933</v>
       </c>
       <c r="Q684">
-        <v>-64.8337915</v>
+        <v>-64.833677</v>
       </c>
     </row>
     <row r="685" xml:space="preserve">
@@ -37862,10 +37862,10 @@
         <v>Yes</v>
       </c>
       <c r="P686">
-        <v>32.2980154</v>
+        <v>32.2956001</v>
       </c>
       <c r="Q686">
-        <v>-64.7950148</v>
+        <v>-64.7900269</v>
       </c>
     </row>
     <row r="687" xml:space="preserve">
@@ -37916,10 +37916,10 @@
         <v>Yes</v>
       </c>
       <c r="P687">
-        <v>32.2978333</v>
+        <v>32.298171</v>
       </c>
       <c r="Q687">
-        <v>-64.8583795</v>
+        <v>-64.859054</v>
       </c>
     </row>
     <row r="688" xml:space="preserve">
@@ -37971,10 +37971,10 @@
         <v>Yes</v>
       </c>
       <c r="P688">
-        <v>32.3046644</v>
+        <v>32.303902</v>
       </c>
       <c r="Q688">
-        <v>-64.8110487</v>
+        <v>-64.811026</v>
       </c>
     </row>
     <row r="689" xml:space="preserve">
@@ -38025,10 +38025,10 @@
         <v>Yes</v>
       </c>
       <c r="P689">
-        <v>32.3150082</v>
+        <v>32.316752</v>
       </c>
       <c r="Q689">
-        <v>-64.7306188</v>
+        <v>-64.73161</v>
       </c>
     </row>
     <row r="690" xml:space="preserve">
@@ -38080,10 +38080,10 @@
         <v>Yes</v>
       </c>
       <c r="P690">
-        <v>32.2960496</v>
+        <v>32.295811</v>
       </c>
       <c r="Q690">
-        <v>-64.867868</v>
+        <v>-64.867647</v>
       </c>
     </row>
     <row r="691" xml:space="preserve">
@@ -38135,10 +38135,10 @@
         <v>Yes</v>
       </c>
       <c r="P691">
-        <v>32.2953597</v>
+        <v>32.294555</v>
       </c>
       <c r="Q691">
-        <v>-64.753873</v>
+        <v>-64.753803</v>
       </c>
     </row>
     <row r="692" xml:space="preserve">
@@ -38190,10 +38190,10 @@
         <v>Yes</v>
       </c>
       <c r="P692">
-        <v>32.2675524</v>
+        <v>32.267609</v>
       </c>
       <c r="Q692">
-        <v>-64.8130835</v>
+        <v>-64.81484</v>
       </c>
     </row>
     <row r="693" xml:space="preserve">
@@ -38244,10 +38244,10 @@
         <v>Yes</v>
       </c>
       <c r="P693">
-        <v>32.30576</v>
+        <v>32.305804</v>
       </c>
       <c r="Q693">
-        <v>-64.8077311</v>
+        <v>-64.807741</v>
       </c>
     </row>
     <row r="694" xml:space="preserve">
@@ -38406,10 +38406,10 @@
         <v>Yes</v>
       </c>
       <c r="P696">
-        <v>32.2941169</v>
+        <v>32.293739</v>
       </c>
       <c r="Q696">
-        <v>-64.7553714</v>
+        <v>-64.754742</v>
       </c>
     </row>
     <row r="697" xml:space="preserve">
@@ -38515,10 +38515,10 @@
         <v>Yes</v>
       </c>
       <c r="P698">
-        <v>32.2992718</v>
+        <v>32.299362</v>
       </c>
       <c r="Q698">
-        <v>-64.7968887</v>
+        <v>-64.797549</v>
       </c>
     </row>
     <row r="699" xml:space="preserve">
@@ -38570,10 +38570,10 @@
         <v>Yes</v>
       </c>
       <c r="P699">
-        <v>32.3038162</v>
+        <v>32.3033237</v>
       </c>
       <c r="Q699">
-        <v>-64.8661288</v>
+        <v>-64.8640225</v>
       </c>
     </row>
     <row r="700" xml:space="preserve">
@@ -38624,10 +38624,10 @@
         <v>Yes</v>
       </c>
       <c r="P700">
-        <v>32.2749053</v>
+        <v>32.274754</v>
       </c>
       <c r="Q700">
-        <v>-64.7848039</v>
+        <v>-64.784855</v>
       </c>
     </row>
     <row r="701" xml:space="preserve">
@@ -38679,10 +38679,10 @@
         <v>Yes</v>
       </c>
       <c r="P701">
-        <v>32.2972364</v>
+        <v>32.297097</v>
       </c>
       <c r="Q701">
-        <v>-64.864622</v>
+        <v>-64.864832</v>
       </c>
     </row>
     <row r="702" xml:space="preserve">
@@ -38787,10 +38787,10 @@
         <v>Yes</v>
       </c>
       <c r="P703">
-        <v>32.3794697</v>
+        <v>32.379419</v>
       </c>
       <c r="Q703">
-        <v>-64.6821691</v>
+        <v>-64.682268</v>
       </c>
     </row>
     <row r="704" xml:space="preserve">
@@ -38841,10 +38841,10 @@
         <v>Yes</v>
       </c>
       <c r="P704">
-        <v>32.3173188</v>
+        <v>32.317401</v>
       </c>
       <c r="Q704">
-        <v>-64.7248862</v>
+        <v>-64.72551</v>
       </c>
     </row>
     <row r="705" xml:space="preserve">
@@ -38951,10 +38951,10 @@
         <v>Yes</v>
       </c>
       <c r="P706">
-        <v>32.3158359</v>
+        <v>32.316404</v>
       </c>
       <c r="Q706">
-        <v>-64.7260153</v>
+        <v>-64.726281</v>
       </c>
     </row>
     <row r="707" xml:space="preserve">
@@ -39062,10 +39062,10 @@
         <v>Yes</v>
       </c>
       <c r="P708">
-        <v>32.2883305</v>
+        <v>32.287818</v>
       </c>
       <c r="Q708">
-        <v>-64.7623112</v>
+        <v>-64.761253</v>
       </c>
     </row>
     <row r="709" xml:space="preserve">
@@ -39172,10 +39172,10 @@
         <v>Yes</v>
       </c>
       <c r="P710">
-        <v>32.3315121</v>
+        <v>32.3375</v>
       </c>
       <c r="Q710">
-        <v>-64.7112575</v>
+        <v>-64.70222</v>
       </c>
     </row>
     <row r="711" xml:space="preserve">
@@ -39336,10 +39336,10 @@
         <v>Yes</v>
       </c>
       <c r="P713">
-        <v>32.2638422</v>
+        <v>32.264297</v>
       </c>
       <c r="Q713">
-        <v>-64.8280954</v>
+        <v>-64.829422</v>
       </c>
     </row>
     <row r="714" xml:space="preserve">
@@ -39390,10 +39390,10 @@
         <v>Yes</v>
       </c>
       <c r="P714">
-        <v>32.3207178</v>
+        <v>32.320359</v>
       </c>
       <c r="Q714">
-        <v>-64.7343399</v>
+        <v>-64.734391</v>
       </c>
     </row>
     <row r="715" xml:space="preserve">
@@ -39445,10 +39445,10 @@
         <v>Yes</v>
       </c>
       <c r="P715">
-        <v>32.320359</v>
+        <v>32.311896</v>
       </c>
       <c r="Q715">
-        <v>-64.734391</v>
+        <v>-64.740743</v>
       </c>
     </row>
     <row r="716" xml:space="preserve">
@@ -39499,10 +39499,10 @@
         <v>Yes</v>
       </c>
       <c r="P716">
-        <v>32.3497189</v>
+        <v>32.34978</v>
       </c>
       <c r="Q716">
-        <v>-64.7174361</v>
+        <v>-64.717458</v>
       </c>
     </row>
     <row r="717" xml:space="preserve">
@@ -39553,10 +39553,10 @@
         <v>Yes</v>
       </c>
       <c r="P717">
-        <v>32.2857086</v>
+        <v>32.287477</v>
       </c>
       <c r="Q717">
-        <v>-64.7734863</v>
+        <v>-64.776819</v>
       </c>
     </row>
     <row r="718" xml:space="preserve">
@@ -39662,10 +39662,10 @@
         <v>Yes</v>
       </c>
       <c r="P719">
-        <v>32.2698887</v>
+        <v>32.269559</v>
       </c>
       <c r="Q719">
-        <v>-64.7924177</v>
+        <v>-64.792222</v>
       </c>
     </row>
     <row r="720" xml:space="preserve">
@@ -39716,10 +39716,10 @@
         <v>Yes</v>
       </c>
       <c r="P720">
-        <v>32.269559</v>
+        <v>32.2678602</v>
       </c>
       <c r="Q720">
-        <v>-64.792222</v>
+        <v>-64.8053367</v>
       </c>
     </row>
     <row r="721" xml:space="preserve">
@@ -39772,10 +39772,10 @@
         <v>Yes</v>
       </c>
       <c r="P721">
-        <v>32.287765</v>
+        <v>32.287286</v>
       </c>
       <c r="Q721">
-        <v>-64.8723049</v>
+        <v>-64.871772</v>
       </c>
     </row>
     <row r="722" xml:space="preserve">
@@ -39881,10 +39881,10 @@
         <v>Yes</v>
       </c>
       <c r="P723">
-        <v>32.2675592</v>
+        <v>32.268846</v>
       </c>
       <c r="Q723">
-        <v>-64.8127731</v>
+        <v>-64.81404</v>
       </c>
     </row>
     <row r="724" xml:space="preserve">
@@ -39935,10 +39935,10 @@
         <v>Yes</v>
       </c>
       <c r="P724">
-        <v>32.2963374</v>
+        <v>32.29622</v>
       </c>
       <c r="Q724">
-        <v>-64.7907181</v>
+        <v>-64.791261</v>
       </c>
     </row>
     <row r="725" xml:space="preserve">
@@ -39989,10 +39989,10 @@
         <v>Yes</v>
       </c>
       <c r="P725">
-        <v>32.3051634</v>
+        <v>32.306233</v>
       </c>
       <c r="Q725">
-        <v>-64.7473652</v>
+        <v>-64.747165</v>
       </c>
     </row>
     <row r="726" xml:space="preserve">
@@ -40043,10 +40043,10 @@
         <v>Yes</v>
       </c>
       <c r="P726">
-        <v>32.3055571</v>
+        <v>32.305576</v>
       </c>
       <c r="Q726">
-        <v>-64.8125711</v>
+        <v>-64.811304</v>
       </c>
     </row>
     <row r="727" xml:space="preserve">
@@ -40151,10 +40151,10 @@
         <v>Yes</v>
       </c>
       <c r="P728">
-        <v>32.3003681</v>
+        <v>32.30135</v>
       </c>
       <c r="Q728">
-        <v>-64.8069823</v>
+        <v>-64.80713</v>
       </c>
     </row>
     <row r="729" xml:space="preserve">
@@ -40205,10 +40205,10 @@
         <v>Yes</v>
       </c>
       <c r="P729">
-        <v>32.299119</v>
+        <v>32.299264</v>
       </c>
       <c r="Q729">
-        <v>-64.7774612</v>
+        <v>-64.776518</v>
       </c>
     </row>
     <row r="730" xml:space="preserve">
@@ -40259,10 +40259,10 @@
         <v>Yes</v>
       </c>
       <c r="P730">
-        <v>32.3169507</v>
+        <v>32.3174</v>
       </c>
       <c r="Q730">
-        <v>-64.7174564</v>
+        <v>-64.71706</v>
       </c>
     </row>
     <row r="731" xml:space="preserve">
@@ -40314,10 +40314,10 @@
         <v>Yes</v>
       </c>
       <c r="P731">
-        <v>32.2537534</v>
+        <v>32.253093</v>
       </c>
       <c r="Q731">
-        <v>-64.8320562</v>
+        <v>-64.832558</v>
       </c>
     </row>
     <row r="732" xml:space="preserve">
@@ -40369,10 +40369,10 @@
         <v>Yes</v>
       </c>
       <c r="P732">
-        <v>32.2593703</v>
+        <v>32.259001</v>
       </c>
       <c r="Q732">
-        <v>-64.8670377</v>
+        <v>-64.867151</v>
       </c>
     </row>
     <row r="733" xml:space="preserve">
@@ -40423,10 +40423,10 @@
         <v>Yes</v>
       </c>
       <c r="P733">
-        <v>32.2981099</v>
+        <v>32.296348</v>
       </c>
       <c r="Q733">
-        <v>-64.8032879</v>
+        <v>-64.801174</v>
       </c>
     </row>
     <row r="734" xml:space="preserve">
@@ -40536,10 +40536,10 @@
         <v>Yes</v>
       </c>
       <c r="P735">
-        <v>32.319302</v>
+        <v>32.3161713</v>
       </c>
       <c r="Q735">
-        <v>-64.728991</v>
+        <v>-64.7224279</v>
       </c>
     </row>
     <row r="736" xml:space="preserve">
@@ -40645,10 +40645,10 @@
         <v>Yes</v>
       </c>
       <c r="P737">
-        <v>32.3035843</v>
+        <v>32.303301</v>
       </c>
       <c r="Q737">
-        <v>-64.7510882</v>
+        <v>-64.750517</v>
       </c>
     </row>
     <row r="738" xml:space="preserve">
@@ -40699,10 +40699,10 @@
         <v>Yes</v>
       </c>
       <c r="P738">
-        <v>32.333877</v>
+        <v>32.333529</v>
       </c>
       <c r="Q738">
-        <v>-64.7408822</v>
+        <v>-64.740664</v>
       </c>
     </row>
     <row r="739" xml:space="preserve">
@@ -40753,10 +40753,10 @@
         <v>Yes</v>
       </c>
       <c r="P739">
-        <v>32.2900621</v>
+        <v>32.290852</v>
       </c>
       <c r="Q739">
-        <v>-64.7690962</v>
+        <v>-64.769715</v>
       </c>
     </row>
     <row r="740" xml:space="preserve">
@@ -40807,10 +40807,10 @@
         <v>Yes</v>
       </c>
       <c r="P740">
-        <v>32.290852</v>
+        <v>32.278925</v>
       </c>
       <c r="Q740">
-        <v>-64.769715</v>
+        <v>-64.773151</v>
       </c>
     </row>
     <row r="741" xml:space="preserve">
@@ -40970,11 +40970,11 @@
       <c r="O743" t="str">
         <v>Yes</v>
       </c>
-      <c r="P743" t="str">
-        <v>32.291840433333334</v>
+      <c r="P743">
+        <v>32.2857086</v>
       </c>
       <c r="Q743">
-        <v>-64.7637586333333</v>
+        <v>-64.7734863</v>
       </c>
     </row>
     <row r="744" xml:space="preserve">
@@ -41025,10 +41025,10 @@
         <v>Yes</v>
       </c>
       <c r="P744">
-        <v>32.3410324</v>
+        <v>32.339728</v>
       </c>
       <c r="Q744">
-        <v>-64.7316682</v>
+        <v>-64.72997</v>
       </c>
     </row>
     <row r="745" xml:space="preserve">
@@ -41133,10 +41133,10 @@
         <v>Yes</v>
       </c>
       <c r="P746">
-        <v>32.3375102</v>
+        <v>32.338238</v>
       </c>
       <c r="Q746">
-        <v>-64.67754</v>
+        <v>-64.676265</v>
       </c>
     </row>
     <row r="747" xml:space="preserve">
@@ -41242,10 +41242,10 @@
         <v>Yes</v>
       </c>
       <c r="P748">
-        <v>32.2519993</v>
+        <v>32.251447</v>
       </c>
       <c r="Q748">
-        <v>-64.8423243</v>
+        <v>-64.841925</v>
       </c>
     </row>
     <row r="749" xml:space="preserve">
@@ -41296,10 +41296,10 @@
         <v>Yes</v>
       </c>
       <c r="P749">
-        <v>32.251447</v>
+        <v>32.2512559</v>
       </c>
       <c r="Q749">
-        <v>-64.841925</v>
+        <v>-64.8443265</v>
       </c>
     </row>
     <row r="750" xml:space="preserve">
@@ -41573,10 +41573,10 @@
         <v>Yes</v>
       </c>
       <c r="P754">
-        <v>32.312204</v>
+        <v>32.3056539905629</v>
       </c>
       <c r="Q754">
-        <v>-64.7566466</v>
+        <v>-64.78817544197068</v>
       </c>
     </row>
     <row r="755" xml:space="preserve">
@@ -41630,10 +41630,10 @@
         <v>Yes</v>
       </c>
       <c r="P755">
-        <v>32.2646449</v>
+        <v>32.264409</v>
       </c>
       <c r="Q755">
-        <v>-64.8185802</v>
+        <v>-64.817993</v>
       </c>
     </row>
     <row r="756" xml:space="preserve">
@@ -41799,10 +41799,10 @@
         <v>Yes</v>
       </c>
       <c r="P758">
-        <v>32.2985147</v>
+        <v>32.298309</v>
       </c>
       <c r="Q758">
-        <v>-64.7947401</v>
+        <v>-64.794108</v>
       </c>
     </row>
     <row r="759" xml:space="preserve">
@@ -41964,10 +41964,10 @@
         <v>Yes</v>
       </c>
       <c r="P761">
-        <v>32.2657219</v>
+        <v>32.265267</v>
       </c>
       <c r="Q761">
-        <v>-64.800233</v>
+        <v>-64.800734</v>
       </c>
     </row>
     <row r="762" xml:space="preserve">
@@ -42078,10 +42078,10 @@
         <v>Yes</v>
       </c>
       <c r="P763">
-        <v>32.2499162</v>
+        <v>32.250044</v>
       </c>
       <c r="Q763">
-        <v>-64.8305295</v>
+        <v>-64.829252</v>
       </c>
     </row>
     <row r="764" xml:space="preserve">
@@ -42188,10 +42188,10 @@
         <v>Yes</v>
       </c>
       <c r="P765">
-        <v>32.28383</v>
+        <v>32.280359</v>
       </c>
       <c r="Q765">
-        <v>-64.7866553</v>
+        <v>-64.791405</v>
       </c>
     </row>
     <row r="766" xml:space="preserve">
@@ -42244,10 +42244,10 @@
         <v>Yes</v>
       </c>
       <c r="P766">
-        <v>32.299973</v>
+        <v>32.299717</v>
       </c>
       <c r="Q766">
-        <v>-64.7464361</v>
+        <v>-64.747314</v>
       </c>
     </row>
     <row r="767" xml:space="preserve">
@@ -42299,10 +42299,10 @@
         <v>Yes</v>
       </c>
       <c r="P767">
-        <v>32.3357651</v>
+        <v>32.335754</v>
       </c>
       <c r="Q767">
-        <v>-64.7366591</v>
+        <v>-64.736608</v>
       </c>
     </row>
     <row r="768" xml:space="preserve">
@@ -42354,10 +42354,10 @@
         <v>Yes</v>
       </c>
       <c r="P768">
-        <v>32.3169507</v>
+        <v>32.317248</v>
       </c>
       <c r="Q768">
-        <v>-64.7174564</v>
+        <v>-64.716717</v>
       </c>
     </row>
     <row r="769" xml:space="preserve">
@@ -42409,10 +42409,10 @@
         <v>Yes</v>
       </c>
       <c r="P769">
-        <v>32.2651982</v>
+        <v>32.2650444</v>
       </c>
       <c r="Q769">
-        <v>-64.8162717</v>
+        <v>-64.8161718</v>
       </c>
     </row>
     <row r="770" xml:space="preserve">
@@ -42463,10 +42463,10 @@
         <v>Yes</v>
       </c>
       <c r="P770">
-        <v>32.252365</v>
+        <v>32.250949</v>
       </c>
       <c r="Q770">
-        <v>-64.8395585</v>
+        <v>-64.843562</v>
       </c>
     </row>
     <row r="771" xml:space="preserve">
@@ -42628,10 +42628,10 @@
         <v>Yes</v>
       </c>
       <c r="P773">
-        <v>32.3022822</v>
+        <v>32.302365</v>
       </c>
       <c r="Q773">
-        <v>-64.8018259</v>
+        <v>-64.8018544</v>
       </c>
     </row>
     <row r="774" xml:space="preserve">
@@ -42682,10 +42682,10 @@
         <v>Yes</v>
       </c>
       <c r="P774">
-        <v>32.3181969</v>
+        <v>32.320632</v>
       </c>
       <c r="Q774">
-        <v>-64.7248279</v>
+        <v>-64.72602</v>
       </c>
     </row>
     <row r="775" xml:space="preserve">
@@ -42792,10 +42792,10 @@
         <v>Yes</v>
       </c>
       <c r="P776">
-        <v>32.3123045</v>
+        <v>32.3122977</v>
       </c>
       <c r="Q776">
-        <v>-64.7552028</v>
+        <v>-64.7551709</v>
       </c>
     </row>
     <row r="777" xml:space="preserve">
@@ -42903,10 +42903,10 @@
         <v>Yes</v>
       </c>
       <c r="P778">
-        <v>32.2646449</v>
+        <v>32.26494</v>
       </c>
       <c r="Q778">
-        <v>-64.8185802</v>
+        <v>-64.820282</v>
       </c>
     </row>
     <row r="779" xml:space="preserve">
@@ -42957,10 +42957,10 @@
         <v>Yes</v>
       </c>
       <c r="P779">
-        <v>32.3383547</v>
+        <v>32.324809</v>
       </c>
       <c r="Q779">
-        <v>-64.7392782</v>
+        <v>-64.741325</v>
       </c>
     </row>
     <row r="780" xml:space="preserve">
@@ -43175,10 +43175,10 @@
         <v>Yes</v>
       </c>
       <c r="P783">
-        <v>32.3333949</v>
+        <v>32.3333906</v>
       </c>
       <c r="Q783">
-        <v>-64.6941855</v>
+        <v>-64.6942276</v>
       </c>
     </row>
     <row r="784" xml:space="preserve">
@@ -43230,10 +43230,10 @@
         <v>Yes</v>
       </c>
       <c r="P784">
-        <v>32.2557445</v>
+        <v>32.2564621</v>
       </c>
       <c r="Q784">
-        <v>-64.8707765</v>
+        <v>-64.869504</v>
       </c>
     </row>
     <row r="785" xml:space="preserve">
@@ -43339,10 +43339,10 @@
         <v/>
       </c>
       <c r="P786">
-        <v>32.359139</v>
+        <v>32.3008022</v>
       </c>
       <c r="Q786">
-        <v>-64.685694</v>
+        <v>-64.7915912</v>
       </c>
     </row>
     <row r="787" xml:space="preserve">
@@ -43447,10 +43447,10 @@
         <v>Yes</v>
       </c>
       <c r="P788">
-        <v>32.3315121</v>
+        <v>32.3375</v>
       </c>
       <c r="Q788">
-        <v>-64.7112575</v>
+        <v>-64.70222</v>
       </c>
     </row>
     <row r="789">

--- a/server/data/Solar Panel Application 2019-now.xlsx
+++ b/server/data/Solar Panel Application 2019-now.xlsx
@@ -35753,10 +35753,10 @@
         <v>Yes</v>
       </c>
       <c r="P648">
-        <v>32.3008022</v>
+        <v>32.273322</v>
       </c>
       <c r="Q648">
-        <v>-64.7915912</v>
+        <v>-64.806901</v>
       </c>
     </row>
     <row r="649" xml:space="preserve">
@@ -43339,10 +43339,10 @@
         <v/>
       </c>
       <c r="P786">
-        <v>32.3008022</v>
+        <v>32.359139</v>
       </c>
       <c r="Q786">
-        <v>-64.7915912</v>
+        <v>-64.685694</v>
       </c>
     </row>
     <row r="787" xml:space="preserve">

--- a/server/data/Solar Panel Application 2019-now.xlsx
+++ b/server/data/Solar Panel Application 2019-now.xlsx
@@ -568,10 +568,10 @@
         <v>Yes</v>
       </c>
       <c r="P2">
-        <v>32.3632247</v>
+        <v>32.371716</v>
       </c>
       <c r="Q2">
-        <v>-64.6778274</v>
+        <v>-64.6645257</v>
       </c>
     </row>
     <row r="3" xml:space="preserve">

--- a/server/data/Solar Panel Application 2019-now.xlsx
+++ b/server/data/Solar Panel Application 2019-now.xlsx
@@ -2031,10 +2031,10 @@
         <v>Yes</v>
       </c>
       <c r="P29">
-        <v>32.2544361</v>
+        <v>32.260736</v>
       </c>
       <c r="Q29">
-        <v>-64.8439449</v>
+        <v>-64.830029</v>
       </c>
     </row>
     <row r="30" xml:space="preserve">
@@ -3338,10 +3338,10 @@
         <v>Yes</v>
       </c>
       <c r="P53">
-        <v>32.2849567</v>
+        <v>32.282623</v>
       </c>
       <c r="Q53">
-        <v>-64.7753406</v>
+        <v>-64.800339</v>
       </c>
     </row>
     <row r="54" xml:space="preserve">
@@ -3446,10 +3446,10 @@
         <v>Yes</v>
       </c>
       <c r="P55">
-        <v>32.2849567</v>
+        <v>32.282095</v>
       </c>
       <c r="Q55">
-        <v>-64.7753406</v>
+        <v>-64.801389</v>
       </c>
     </row>
     <row r="56" xml:space="preserve">
@@ -5503,10 +5503,10 @@
         <v>Yes</v>
       </c>
       <c r="P93">
-        <v>32.2678602</v>
+        <v>32.273048</v>
       </c>
       <c r="Q93">
-        <v>-64.8053367</v>
+        <v>-64.794697</v>
       </c>
     </row>
     <row r="94" xml:space="preserve">
@@ -7523,10 +7523,10 @@
         <v>Yes</v>
       </c>
       <c r="P130">
-        <v>32.2678602</v>
+        <v>32.265839</v>
       </c>
       <c r="Q130">
-        <v>-64.8053367</v>
+        <v>-64.829075</v>
       </c>
     </row>
     <row r="131" xml:space="preserve">
@@ -8765,10 +8765,10 @@
         <v>Yes</v>
       </c>
       <c r="P153">
-        <v>32.3632247</v>
+        <v>32.368196</v>
       </c>
       <c r="Q153">
-        <v>-64.6778274</v>
+        <v>-64.673791</v>
       </c>
     </row>
     <row r="154" xml:space="preserve">
@@ -9252,10 +9252,10 @@
         <v>Yes</v>
       </c>
       <c r="P162">
-        <v>32.3412801</v>
+        <v>32.333328</v>
       </c>
       <c r="Q162">
-        <v>-64.7255713</v>
+        <v>-64.727405</v>
       </c>
     </row>
     <row r="163" xml:space="preserve">
@@ -9524,10 +9524,10 @@
         <v>Yes</v>
       </c>
       <c r="P167">
-        <v>32.2849567</v>
+        <v>32.281492</v>
       </c>
       <c r="Q167">
-        <v>-64.7753406</v>
+        <v>-64.80354</v>
       </c>
     </row>
     <row r="168" xml:space="preserve">
@@ -9578,10 +9578,10 @@
         <v>Yes</v>
       </c>
       <c r="P168">
-        <v>32.3008022</v>
+        <v>32.296397</v>
       </c>
       <c r="Q168">
-        <v>-64.7915912</v>
+        <v>-64.799038</v>
       </c>
     </row>
     <row r="169" xml:space="preserve">
@@ -13600,10 +13600,10 @@
         <v>Yes</v>
       </c>
       <c r="P242">
-        <v>32.3412801</v>
+        <v>32.3375</v>
       </c>
       <c r="Q242">
-        <v>-64.7255713</v>
+        <v>-64.70222</v>
       </c>
     </row>
     <row r="243" xml:space="preserve">
@@ -17128,10 +17128,10 @@
         <v>Yes</v>
       </c>
       <c r="P307">
-        <v>32.2678602</v>
+        <v>32.263842</v>
       </c>
       <c r="Q307">
-        <v>-64.8053367</v>
+        <v>-64.821897</v>
       </c>
     </row>
     <row r="308" xml:space="preserve">
@@ -20538,10 +20538,10 @@
         <v>Yes</v>
       </c>
       <c r="P370">
-        <v>32.2678602</v>
+        <v>32.265839</v>
       </c>
       <c r="Q370">
-        <v>-64.8053367</v>
+        <v>-64.829075</v>
       </c>
     </row>
     <row r="371" xml:space="preserve">
@@ -21246,10 +21246,10 @@
         <v>Yes</v>
       </c>
       <c r="P383">
-        <v>32.2846631</v>
+        <v>32.288659</v>
       </c>
       <c r="Q383">
-        <v>-64.8752028</v>
+        <v>-64.874039</v>
       </c>
     </row>
     <row r="384" xml:space="preserve">
@@ -22070,10 +22070,10 @@
         <v>Yes</v>
       </c>
       <c r="P398">
-        <v>32.2678602</v>
+        <v>32.269346975</v>
       </c>
       <c r="Q398">
-        <v>-64.8053367</v>
+        <v>-64.807804025</v>
       </c>
     </row>
     <row r="399" xml:space="preserve">
@@ -23365,11 +23365,11 @@
       <c r="O422" t="str">
         <v>Yes</v>
       </c>
-      <c r="P422">
-        <v>32.3008022</v>
+      <c r="P422" t="str">
+        <v>32.29370414931507</v>
       </c>
       <c r="Q422">
-        <v>-64.7915912</v>
+        <v>-64.8038436136986</v>
       </c>
     </row>
     <row r="423" xml:space="preserve">
@@ -27597,10 +27597,10 @@
         <v>Yes</v>
       </c>
       <c r="P500">
-        <v>32.2678602</v>
+        <v>32.293934</v>
       </c>
       <c r="Q500">
-        <v>-64.8053367</v>
+        <v>-64.769054</v>
       </c>
     </row>
     <row r="501" xml:space="preserve">
@@ -28741,10 +28741,10 @@
         <v>Yes</v>
       </c>
       <c r="P521">
-        <v>32.3154757</v>
+        <v>32.248964</v>
       </c>
       <c r="Q521">
-        <v>-64.7304162</v>
+        <v>-64.839529</v>
       </c>
     </row>
     <row r="522" xml:space="preserve">
@@ -28795,10 +28795,10 @@
         <v>Yes</v>
       </c>
       <c r="P522">
-        <v>32.2544361</v>
+        <v>32.306196</v>
       </c>
       <c r="Q522">
-        <v>-64.8439449</v>
+        <v>-64.735474</v>
       </c>
     </row>
     <row r="523" xml:space="preserve">
@@ -29120,10 +29120,10 @@
         <v>Yes</v>
       </c>
       <c r="P528">
-        <v>32.2678602</v>
+        <v>32.296333</v>
       </c>
       <c r="Q528">
-        <v>-64.8053367</v>
+        <v>-64.75155</v>
       </c>
     </row>
     <row r="529" xml:space="preserve">
@@ -30214,10 +30214,10 @@
         <v>Yes</v>
       </c>
       <c r="P548">
-        <v>32.2849567</v>
+        <v>32.302098</v>
       </c>
       <c r="Q548">
-        <v>-64.7753406</v>
+        <v>-64.761213</v>
       </c>
     </row>
     <row r="549" xml:space="preserve">
@@ -33049,10 +33049,10 @@
         <v>Yes</v>
       </c>
       <c r="P599">
-        <v>32.3412801</v>
+        <v>32.297044</v>
       </c>
       <c r="Q599">
-        <v>-64.7255713</v>
+        <v>-64.863524</v>
       </c>
     </row>
     <row r="600" xml:space="preserve">
@@ -33766,10 +33766,10 @@
         <v>Yes</v>
       </c>
       <c r="P612">
-        <v>32.2678602</v>
+        <v>32.368971</v>
       </c>
       <c r="Q612">
-        <v>-64.8053367</v>
+        <v>-64.681281</v>
       </c>
     </row>
     <row r="613" xml:space="preserve">
@@ -33822,10 +33822,10 @@
         <v>Yes</v>
       </c>
       <c r="P613">
-        <v>32.2678602</v>
+        <v>32.283819</v>
       </c>
       <c r="Q613">
-        <v>-64.8053367</v>
+        <v>-64.80844</v>
       </c>
     </row>
     <row r="614" xml:space="preserve">
@@ -33931,10 +33931,10 @@
         <v>Yes</v>
       </c>
       <c r="P615">
-        <v>32.2678602</v>
+        <v>32.337896</v>
       </c>
       <c r="Q615">
-        <v>-64.8053367</v>
+        <v>-64.701341</v>
       </c>
     </row>
     <row r="616" xml:space="preserve">
@@ -34255,10 +34255,10 @@
         <v>Yes</v>
       </c>
       <c r="P621">
-        <v>32.2678602</v>
+        <v>32.284683</v>
       </c>
       <c r="Q621">
-        <v>-64.8053367</v>
+        <v>-64.87527</v>
       </c>
     </row>
     <row r="622" xml:space="preserve">
@@ -34915,10 +34915,10 @@
         <v>Yes</v>
       </c>
       <c r="P633">
-        <v>32.3008022</v>
+        <v>32.306537</v>
       </c>
       <c r="Q633">
-        <v>-64.7915912</v>
+        <v>-64.737434</v>
       </c>
     </row>
     <row r="634" xml:space="preserve">
@@ -35706,10 +35706,10 @@
         <v>Yes</v>
       </c>
       <c r="P647">
-        <v>32.2849567</v>
+        <v>32.298704</v>
       </c>
       <c r="Q647">
-        <v>-64.7753406</v>
+        <v>-64.755451</v>
       </c>
     </row>
     <row r="648" xml:space="preserve">
@@ -38404,10 +38404,10 @@
         <v>Yes</v>
       </c>
       <c r="P696">
-        <v>32.2678602</v>
+        <v>32.317401</v>
       </c>
       <c r="Q696">
-        <v>-64.8053367</v>
+        <v>-64.72551</v>
       </c>
     </row>
     <row r="697" xml:space="preserve">
@@ -40533,10 +40533,10 @@
         <v>Yes</v>
       </c>
       <c r="P735">
-        <v>32.2678602</v>
+        <v>32.339728</v>
       </c>
       <c r="Q735">
-        <v>-64.8053367</v>
+        <v>-64.72997</v>
       </c>
     </row>
     <row r="736" xml:space="preserve">
@@ -40916,10 +40916,10 @@
         <v>Yes</v>
       </c>
       <c r="P742">
-        <v>32.3154757</v>
+        <v>32.29434</v>
       </c>
       <c r="Q742">
-        <v>-64.7304162</v>
+        <v>-64.774311</v>
       </c>
     </row>
     <row r="743" xml:space="preserve">
@@ -41474,10 +41474,10 @@
         <v>Yes</v>
       </c>
       <c r="P752">
-        <v>32.2544361</v>
+        <v>32.265453</v>
       </c>
       <c r="Q752">
-        <v>-64.8439449</v>
+        <v>-64.800223</v>
       </c>
     </row>
     <row r="753" xml:space="preserve">
